--- a/Faculties/Natural Science/Postgrad Modules Natural Science.xlsx
+++ b/Faculties/Natural Science/Postgrad Modules Natural Science.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d24d4a286855a075/Desktop/Team_6_repo/Team19/Faculties/Natural Science/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mwamb\OneDrive\Desktop\Team_6_repo\Team19\Faculties\Natural Science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_F25DC773A252ABDACC10480281DB6CA25BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5AC076D4-8F5B-4114-977C-6C98B074084E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09881E10-78C0-44E2-94C9-6677A295E75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1383,45 +1383,6 @@
     <t>Master of Clinical Pharmacy 3852</t>
   </si>
   <si>
-    <t>BScHons  Applied Geology  3710</t>
-  </si>
-  <si>
-    <t>BScHons  Astrophysics  3793</t>
-  </si>
-  <si>
-    <t>BScHons  Astrophysics  3793, BScHons  Physical Science  3714</t>
-  </si>
-  <si>
-    <t>BScHons  Biodiversity and Conservation Biology  3731</t>
-  </si>
-  <si>
-    <t>BScHons  Biotechnology  3707</t>
-  </si>
-  <si>
-    <t>BScHons  Biotechnology  3707, BScHons  Medical Bioscience  3721</t>
-  </si>
-  <si>
-    <t>BScHons  Chemistry  3734</t>
-  </si>
-  <si>
-    <t>PGDip  Computer and Media Application  1627</t>
-  </si>
-  <si>
-    <t>BScHons  Statistical Science  3737, BScHons  Computational Finance  3739</t>
-  </si>
-  <si>
-    <t>BScHons  Mathematical Science  3736, BScHons  Computational Finance  3739</t>
-  </si>
-  <si>
-    <t>BScHons  Computational Finance  3739, BScHons  Statistical Science  3737</t>
-  </si>
-  <si>
-    <t>BScHons  Computer Science  3735</t>
-  </si>
-  <si>
-    <t>BScHons  Computer Science  3735, BScHons  Statistical Science  3737</t>
-  </si>
-  <si>
     <t xml:space="preserve">Computer Science 737  Artificial Intelligence </t>
   </si>
   <si>
@@ -1443,78 +1404,15 @@
     <t xml:space="preserve">Computer Science 743  Adv Immersive Tech </t>
   </si>
   <si>
-    <t>BScHons  Environment and Water Science  3780</t>
-  </si>
-  <si>
-    <t>BScHons  Mathematical Science  3736</t>
-  </si>
-  <si>
-    <t>BScHons  Mathematical Science  3736, BScHons  Statistical Science  3737</t>
-  </si>
-  <si>
-    <t>BScHons  Mathematical Science  3736, BScHons  Computational Finance  3739, BScHons  Computer Science  3735</t>
-  </si>
-  <si>
-    <t>BScHons  Mathematical Science  3736, BScHons  Computer Science  3735</t>
-  </si>
-  <si>
-    <t>BScHons  Medical Bioscience  3721</t>
-  </si>
-  <si>
-    <t>BScHons  Physical Science  3714</t>
-  </si>
-  <si>
-    <t>BScHons  Physical Science  3714, BScHons  Computer Science  3735</t>
-  </si>
-  <si>
-    <t>BScHons  Population Studies  3738</t>
-  </si>
-  <si>
-    <t>BScHons  Population Studies  3738, BScHons  Statistical Science  3737</t>
-  </si>
-  <si>
     <t>Research Project  Population Studies  761</t>
   </si>
   <si>
-    <t>BScHons  Population Studies  3738, BScHons  Medical Bioscience  3721</t>
-  </si>
-  <si>
-    <t>BScHons  Statistical Science  3737</t>
-  </si>
-  <si>
     <t xml:space="preserve">STA331, STA332,  STA739 </t>
   </si>
   <si>
-    <t>BScHons  Computational Finance  3739</t>
-  </si>
-  <si>
-    <t>BScHons  Statistical Science  3737, BScHons  Computer Science  3735</t>
-  </si>
-  <si>
-    <t>PGDip  IWRM  3880</t>
-  </si>
-  <si>
     <t>Mini-Thesis  Research Project  803</t>
   </si>
   <si>
-    <t>MSc  Mathematical Science  3849</t>
-  </si>
-  <si>
-    <t>MSc  Statistical Science  3838, MSc  Computational Finance  3093</t>
-  </si>
-  <si>
-    <t>MSc  Computational Finance  3093</t>
-  </si>
-  <si>
-    <t>MPhil  Population Studies  3921, MSc  Statistical Science  3838, MSc  Computational Finance  3093</t>
-  </si>
-  <si>
-    <t>MSc  Computational Finance  3093, MSc  Statistical Science  3838</t>
-  </si>
-  <si>
-    <t>MSc  Nanoscience  3089</t>
-  </si>
-  <si>
     <t>Foundations of Nanobiomedical Science  Non-Bio  813</t>
   </si>
   <si>
@@ -1524,34 +1422,136 @@
     <t>Foundations of Nanophysics  Non-Phys  833</t>
   </si>
   <si>
-    <t>MSc  Pharmacy Admin and Policy Regulation  3859</t>
-  </si>
-  <si>
     <t>Pharmaceutical Care – Adult Medicine  1  815</t>
   </si>
   <si>
     <t>Pharmaceutical Care - Adult Medicine  2  820</t>
   </si>
   <si>
-    <t>MSc  Physical Science  3081</t>
-  </si>
-  <si>
-    <t>MPhil  Population Studies  3921</t>
-  </si>
-  <si>
-    <t>MSc  Statistical Science  3838</t>
-  </si>
-  <si>
-    <t>MSc  Statistical Science  3838, MSc  Computational Finance  3093, MPhil  Population Studies  3921</t>
-  </si>
-  <si>
-    <t>MSc  Statistical Science  3838, MPhil  Population Studies  3921</t>
-  </si>
-  <si>
-    <t>MSc  Statistical Science  3838, MSc  Medical Biosciences  3819, MPhil  Population Studies  3921</t>
-  </si>
-  <si>
-    <t>MSc  Statistical Sciences  3838</t>
+    <t>BScHons Applied Geology 3710</t>
+  </si>
+  <si>
+    <t>BScHons Astrophysics 3793</t>
+  </si>
+  <si>
+    <t>BScHons Astrophysics 3793, BScHons Physical Science 3714</t>
+  </si>
+  <si>
+    <t>BScHons Biodiversity and Conservation Biology 3731</t>
+  </si>
+  <si>
+    <t>BScHons Biotechnology 3707</t>
+  </si>
+  <si>
+    <t>BScHons Biotechnology 3707, BScHons Medical Bioscience 3721</t>
+  </si>
+  <si>
+    <t>BScHons Chemistry 3734</t>
+  </si>
+  <si>
+    <t>PGDip Computer and Media Application 1627</t>
+  </si>
+  <si>
+    <t>BScHons Statistical Science 3737, BScHons Computational Finance 3739</t>
+  </si>
+  <si>
+    <t>BScHons Mathematical Science 3736, BScHons Computational Finance 3739</t>
+  </si>
+  <si>
+    <t>BScHons Computational Finance 3739, BScHons Statistical Science 3737</t>
+  </si>
+  <si>
+    <t>BScHons Computer Science 3735</t>
+  </si>
+  <si>
+    <t>BScHons Computer Science 3735, BScHons Statistical Science 3737</t>
+  </si>
+  <si>
+    <t>BScHons Environment and Water Science 3780</t>
+  </si>
+  <si>
+    <t>BScHons Mathematical Science 3736</t>
+  </si>
+  <si>
+    <t>BScHons Mathematical Science 3736, BScHons Statistical Science 3737</t>
+  </si>
+  <si>
+    <t>BScHons Mathematical Science 3736, BScHons Computational Finance 3739, BScHons Computer Science 3735</t>
+  </si>
+  <si>
+    <t>BScHons Mathematical Science 3736, BScHons Computer Science 3735</t>
+  </si>
+  <si>
+    <t>BScHons Medical Bioscience 3721</t>
+  </si>
+  <si>
+    <t>BScHons Physical Science 3714</t>
+  </si>
+  <si>
+    <t>BScHons Physical Science 3714, BScHons Computer Science 3735</t>
+  </si>
+  <si>
+    <t>BScHons Population Studies 3738</t>
+  </si>
+  <si>
+    <t>BScHons Population Studies 3738, BScHons Statistical Science 3737</t>
+  </si>
+  <si>
+    <t>BScHons Population Studies 3738, BScHons Medical Bioscience 3721</t>
+  </si>
+  <si>
+    <t>BScHons Statistical Science 3737</t>
+  </si>
+  <si>
+    <t>BScHons Computational Finance 3739</t>
+  </si>
+  <si>
+    <t>BScHons Statistical Science 3737, BScHons Computer Science 3735</t>
+  </si>
+  <si>
+    <t>PGDip IWRM 3880</t>
+  </si>
+  <si>
+    <t>MSc Mathematical Science 3849</t>
+  </si>
+  <si>
+    <t>MSc Statistical Science 3838, MSc Computational Finance 3093</t>
+  </si>
+  <si>
+    <t>MSc Computational Finance 3093</t>
+  </si>
+  <si>
+    <t>MPhil Population Studies 3921, MSc Statistical Science 3838, MSc Computational Finance 3093</t>
+  </si>
+  <si>
+    <t>MSc Computational Finance 3093, MSc Statistical Science 3838</t>
+  </si>
+  <si>
+    <t>MSc Nanoscience 3089</t>
+  </si>
+  <si>
+    <t>MSc Pharmacy Admin and Policy Regulation 3859</t>
+  </si>
+  <si>
+    <t>MSc Physical Science 3081</t>
+  </si>
+  <si>
+    <t>MPhil Population Studies 3921</t>
+  </si>
+  <si>
+    <t>MSc Statistical Science 3838</t>
+  </si>
+  <si>
+    <t>MSc Statistical Science 3838, MSc Computational Finance 3093, MPhil Population Studies 3921</t>
+  </si>
+  <si>
+    <t>MSc Statistical Science 3838, MPhil Population Studies 3921</t>
+  </si>
+  <si>
+    <t>MSc Statistical Science 3838, MSc Medical Biosciences 3819, MPhil Population Studies 3921</t>
+  </si>
+  <si>
+    <t>MSc Statistical Sciences 3838</t>
   </si>
 </sst>
 </file>
@@ -1923,7 +1923,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
@@ -1943,7 +1943,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>8</v>
@@ -1963,7 +1963,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>8</v>
@@ -1983,7 +1983,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>15</v>
@@ -1992,7 +1992,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>8</v>
@@ -2023,7 +2023,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>8</v>
@@ -2043,7 +2043,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>8</v>
@@ -2052,7 +2052,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>8</v>
@@ -2083,7 +2083,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>8</v>
@@ -2103,7 +2103,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>8</v>
@@ -2112,7 +2112,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>28</v>
       </c>
@@ -2123,7 +2123,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>8</v>
@@ -2143,7 +2143,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>8</v>
@@ -2172,7 +2172,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>34</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>8</v>
@@ -2203,7 +2203,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>8</v>
@@ -2212,7 +2212,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>38</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>8</v>
@@ -2243,7 +2243,7 @@
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>8</v>
@@ -2252,7 +2252,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>42</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>1</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>8</v>
@@ -2272,7 +2272,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>44</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>8</v>
@@ -2292,7 +2292,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>46</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>8</v>
@@ -2312,7 +2312,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>48</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>8</v>
@@ -2332,7 +2332,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>50</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>8</v>
@@ -2352,7 +2352,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>52</v>
       </c>
@@ -2363,7 +2363,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>8</v>
@@ -2372,7 +2372,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>54</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>8</v>
@@ -2392,7 +2392,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>56</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>1</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>8</v>
@@ -2432,7 +2432,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>60</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>1</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>8</v>
@@ -2452,7 +2452,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>62</v>
       </c>
@@ -2463,7 +2463,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>8</v>
@@ -2483,7 +2483,7 @@
         <v>1</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>66</v>
@@ -2492,7 +2492,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>67</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>8</v>
@@ -2512,7 +2512,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>69</v>
       </c>
@@ -2523,7 +2523,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>8</v>
@@ -2543,7 +2543,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>8</v>
@@ -2552,7 +2552,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>73</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>8</v>
@@ -2572,7 +2572,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>75</v>
       </c>
@@ -2583,7 +2583,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>8</v>
@@ -2592,7 +2592,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>77</v>
       </c>
@@ -2603,7 +2603,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>8</v>
@@ -2612,7 +2612,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>79</v>
       </c>
@@ -2623,7 +2623,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>8</v>
@@ -2643,7 +2643,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>8</v>
@@ -2663,7 +2663,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>8</v>
@@ -2703,7 +2703,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>8</v>
@@ -2723,7 +2723,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>8</v>
@@ -2743,7 +2743,7 @@
         <v>1</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>8</v>
@@ -2763,7 +2763,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>8</v>
@@ -2783,7 +2783,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>8</v>
@@ -2803,7 +2803,7 @@
         <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>8</v>
@@ -2812,7 +2812,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>99</v>
       </c>
@@ -2823,7 +2823,7 @@
         <v>46024</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>459</v>
+        <v>474</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>101</v>
@@ -2832,7 +2832,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>102</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>104</v>
@@ -2852,7 +2852,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>105</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>1</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>107</v>
@@ -2872,7 +2872,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>108</v>
       </c>
@@ -2883,7 +2883,7 @@
         <v>1</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>110</v>
@@ -2892,7 +2892,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>111</v>
       </c>
@@ -2903,7 +2903,7 @@
         <v>1</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>8</v>
@@ -2912,7 +2912,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>113</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>1</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>8</v>
@@ -2932,7 +2932,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>115</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>1</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>110</v>
@@ -2952,7 +2952,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>117</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>1</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>119</v>
@@ -2983,7 +2983,7 @@
         <v>1</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>8</v>
@@ -3003,7 +3003,7 @@
         <v>1</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>8</v>
@@ -3012,7 +3012,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>124</v>
       </c>
@@ -3023,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>8</v>
@@ -3043,7 +3043,7 @@
         <v>1</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>8</v>
@@ -3052,7 +3052,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>128</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>1</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>8</v>
@@ -3072,18 +3072,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="C60" s="1">
         <v>1</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>8</v>
@@ -3097,13 +3097,13 @@
         <v>131</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="C61" s="1">
         <v>1</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>8</v>
@@ -3117,13 +3117,13 @@
         <v>132</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="C62" s="1">
         <v>1</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>8</v>
@@ -3137,13 +3137,13 @@
         <v>133</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="C63" s="1">
         <v>1</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>8</v>
@@ -3157,13 +3157,13 @@
         <v>134</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="C64" s="1">
         <v>1</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>135</v>
@@ -3177,13 +3177,13 @@
         <v>136</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="C65" s="1">
         <v>1</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>8</v>
@@ -3197,13 +3197,13 @@
         <v>137</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="C66" s="1">
         <v>1</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>8</v>
@@ -3223,7 +3223,7 @@
         <v>1</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>8</v>
@@ -3243,7 +3243,7 @@
         <v>1</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>8</v>
@@ -3252,7 +3252,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>142</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>1</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>8</v>
@@ -3272,7 +3272,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>144</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>1</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>8</v>
@@ -3292,7 +3292,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>146</v>
       </c>
@@ -3303,7 +3303,7 @@
         <v>1</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>8</v>
@@ -3312,7 +3312,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>148</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>1</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>8</v>
@@ -3343,7 +3343,7 @@
         <v>1</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>8</v>
@@ -3352,7 +3352,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>152</v>
       </c>
@@ -3363,7 +3363,7 @@
         <v>1</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>8</v>
@@ -3372,7 +3372,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>154</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>8</v>
@@ -3403,7 +3403,7 @@
         <v>1</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>8</v>
@@ -3412,7 +3412,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>158</v>
       </c>
@@ -3423,7 +3423,7 @@
         <v>1</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>8</v>
@@ -3432,7 +3432,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="216" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>160</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>1</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>8</v>
@@ -3452,7 +3452,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>162</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>1</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>8</v>
@@ -3483,7 +3483,7 @@
         <v>1</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>8</v>
@@ -3492,7 +3492,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>166</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>1</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>8</v>
@@ -3523,7 +3523,7 @@
         <v>1</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>8</v>
@@ -3532,7 +3532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>170</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>1</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>8</v>
@@ -3552,7 +3552,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>172</v>
       </c>
@@ -3563,7 +3563,7 @@
         <v>1</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>8</v>
@@ -3572,7 +3572,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>174</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>1</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>8</v>
@@ -3592,7 +3592,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>176</v>
       </c>
@@ -3603,7 +3603,7 @@
         <v>1</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>8</v>
@@ -3612,7 +3612,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>178</v>
       </c>
@@ -3623,7 +3623,7 @@
         <v>1</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>8</v>
@@ -3632,7 +3632,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>180</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>1</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>8</v>
@@ -3663,7 +3663,7 @@
         <v>1</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>8</v>
@@ -3683,7 +3683,7 @@
         <v>1</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>8</v>
@@ -3692,7 +3692,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>186</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>1</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>1</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>8</v>
@@ -3743,7 +3743,7 @@
         <v>1</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>8</v>
@@ -3763,7 +3763,7 @@
         <v>1</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>8</v>
@@ -3783,7 +3783,7 @@
         <v>1</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>8</v>
@@ -3803,7 +3803,7 @@
         <v>1</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>8</v>
@@ -3812,7 +3812,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>198</v>
       </c>
@@ -3823,7 +3823,7 @@
         <v>1</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>8</v>
@@ -3843,7 +3843,7 @@
         <v>1</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>8</v>
@@ -3863,7 +3863,7 @@
         <v>1</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>8</v>
@@ -3872,7 +3872,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>204</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>1</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>8</v>
@@ -3892,7 +3892,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>206</v>
       </c>
@@ -3903,7 +3903,7 @@
         <v>1</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>8</v>
@@ -3912,7 +3912,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>208</v>
       </c>
@@ -3923,7 +3923,7 @@
         <v>1</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>8</v>
@@ -3932,7 +3932,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>210</v>
       </c>
@@ -3943,7 +3943,7 @@
         <v>1</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>8</v>
@@ -3952,7 +3952,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>212</v>
       </c>
@@ -3963,7 +3963,7 @@
         <v>1</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>8</v>
@@ -4003,7 +4003,7 @@
         <v>1</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>214</v>
@@ -4012,7 +4012,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>218</v>
       </c>
@@ -4023,7 +4023,7 @@
         <v>1</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>214</v>
@@ -4032,7 +4032,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>220</v>
       </c>
@@ -4043,7 +4043,7 @@
         <v>1</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>8</v>
@@ -4052,7 +4052,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>222</v>
       </c>
@@ -4063,7 +4063,7 @@
         <v>1</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>8</v>
@@ -4072,7 +4072,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>224</v>
       </c>
@@ -4083,7 +4083,7 @@
         <v>1</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>8</v>
@@ -4103,7 +4103,7 @@
         <v>1</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>228</v>
@@ -4112,7 +4112,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>229</v>
       </c>
@@ -4123,7 +4123,7 @@
         <v>1</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>228</v>
@@ -4132,7 +4132,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>231</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>1</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>233</v>
@@ -4152,18 +4152,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>234</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="C114" s="1">
         <v>1</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>8</v>
@@ -4172,7 +4172,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>235</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>1</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>8</v>
@@ -4192,7 +4192,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>237</v>
       </c>
@@ -4203,16 +4203,16 @@
         <v>1</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>485</v>
+        <v>460</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>239</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>1</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>8</v>
@@ -4232,7 +4232,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>241</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>1</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>243</v>
@@ -4252,7 +4252,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>244</v>
       </c>
@@ -4263,7 +4263,7 @@
         <v>1</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>246</v>
@@ -4272,7 +4272,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>247</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>1</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>246</v>
@@ -4292,7 +4292,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>249</v>
       </c>
@@ -4303,7 +4303,7 @@
         <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>251</v>
@@ -4312,7 +4312,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>252</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>1</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>8</v>
@@ -4332,7 +4332,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>254</v>
       </c>
@@ -4343,7 +4343,7 @@
         <v>1</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>8</v>
@@ -4363,7 +4363,7 @@
         <v>1</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>8</v>
@@ -4372,7 +4372,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="125" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>258</v>
       </c>
@@ -4383,7 +4383,7 @@
         <v>1</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>246</v>
@@ -4392,7 +4392,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="126" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>260</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>1</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>8</v>
@@ -4412,7 +4412,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>262</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>1</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>228</v>
@@ -4443,7 +4443,7 @@
         <v>1</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>8</v>
@@ -4463,7 +4463,7 @@
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>8</v>
@@ -4483,7 +4483,7 @@
         <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>8</v>
@@ -4523,7 +4523,7 @@
         <v>1</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>8</v>
@@ -4543,7 +4543,7 @@
         <v>1</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>8</v>
@@ -4563,7 +4563,7 @@
         <v>1</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>8</v>
@@ -4583,7 +4583,7 @@
         <v>1</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>8</v>
@@ -4597,13 +4597,13 @@
         <v>280</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>489</v>
+        <v>461</v>
       </c>
       <c r="C136" s="1">
         <v>1</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>8</v>
@@ -4623,7 +4623,7 @@
         <v>46024</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>8</v>
@@ -4643,7 +4643,7 @@
         <v>46024</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>8</v>
@@ -4652,7 +4652,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="139" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>285</v>
       </c>
@@ -4663,7 +4663,7 @@
         <v>46024</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>8</v>
@@ -4683,7 +4683,7 @@
         <v>46024</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>8</v>
@@ -4703,7 +4703,7 @@
         <v>46024</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>8</v>
@@ -4723,7 +4723,7 @@
         <v>46024</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>8</v>
@@ -4743,7 +4743,7 @@
         <v>46024</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>46024</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>8</v>
@@ -4783,7 +4783,7 @@
         <v>46024</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>8</v>
@@ -4803,7 +4803,7 @@
         <v>46024</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>8</v>
@@ -4823,7 +4823,7 @@
         <v>46024</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>8</v>
@@ -4843,7 +4843,7 @@
         <v>46024</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>8</v>
@@ -4852,7 +4852,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="149" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>305</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>46024</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>107</v>
@@ -4872,7 +4872,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="150" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>307</v>
       </c>
@@ -4883,7 +4883,7 @@
         <v>46024</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>8</v>
@@ -4892,7 +4892,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="151" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>309</v>
       </c>
@@ -4903,7 +4903,7 @@
         <v>46024</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>110</v>
@@ -4912,7 +4912,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="1:6" ht="216" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>311</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>46024</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>104</v>
@@ -4932,7 +4932,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="153" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>313</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>46024</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>110</v>
@@ -4952,7 +4952,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="154" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>315</v>
       </c>
@@ -4963,7 +4963,7 @@
         <v>46024</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>110</v>
@@ -4972,7 +4972,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="155" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>317</v>
       </c>
@@ -4983,7 +4983,7 @@
         <v>46024</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>107</v>
@@ -4992,7 +4992,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="156" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>319</v>
       </c>
@@ -5003,7 +5003,7 @@
         <v>46024</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>321</v>
@@ -5012,7 +5012,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="157" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>322</v>
       </c>
@@ -5023,7 +5023,7 @@
         <v>46024</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>110</v>
@@ -5032,7 +5032,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>324</v>
       </c>
@@ -5043,7 +5043,7 @@
         <v>46024</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>110</v>
@@ -5063,7 +5063,7 @@
         <v>46024</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>8</v>
@@ -5083,7 +5083,7 @@
         <v>46024</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>8</v>
@@ -5103,7 +5103,7 @@
         <v>46024</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>8</v>
@@ -5123,7 +5123,7 @@
         <v>46024</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>8</v>
@@ -5143,7 +5143,7 @@
         <v>46024</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>8</v>
@@ -5157,13 +5157,13 @@
         <v>336</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="C164" s="3">
         <v>46024</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>8</v>
@@ -5183,7 +5183,7 @@
         <v>46024</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>339</v>
@@ -5203,7 +5203,7 @@
         <v>46024</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>342</v>
@@ -5217,13 +5217,13 @@
         <v>343</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>497</v>
+        <v>463</v>
       </c>
       <c r="C167" s="3">
         <v>46024</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>8</v>
@@ -5232,7 +5232,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="168" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>344</v>
       </c>
@@ -5243,7 +5243,7 @@
         <v>46024</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>46024</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>346</v>
@@ -5277,13 +5277,13 @@
         <v>349</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>498</v>
+        <v>464</v>
       </c>
       <c r="C170" s="3">
         <v>46024</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>8</v>
@@ -5292,7 +5292,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="171" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>350</v>
       </c>
@@ -5303,7 +5303,7 @@
         <v>46024</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>8</v>
@@ -5312,7 +5312,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="172" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>352</v>
       </c>
@@ -5323,7 +5323,7 @@
         <v>46024</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>8</v>
@@ -5332,7 +5332,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="173" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>354</v>
       </c>
@@ -5343,7 +5343,7 @@
         <v>46024</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>8</v>
@@ -5352,7 +5352,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="174" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>356</v>
       </c>
@@ -5363,7 +5363,7 @@
         <v>46024</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>8</v>
@@ -5372,7 +5372,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="175" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>358</v>
       </c>
@@ -5383,7 +5383,7 @@
         <v>46024</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>8</v>
@@ -5392,7 +5392,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="176" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>360</v>
       </c>
@@ -5403,7 +5403,7 @@
         <v>46024</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>8</v>
@@ -5412,7 +5412,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>362</v>
       </c>
@@ -5423,7 +5423,7 @@
         <v>46024</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>8</v>
@@ -5432,7 +5432,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="178" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>364</v>
       </c>
@@ -5443,7 +5443,7 @@
         <v>46024</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>8</v>
@@ -5452,7 +5452,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="179" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>366</v>
       </c>
@@ -5463,7 +5463,7 @@
         <v>46024</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>8</v>
@@ -5472,7 +5472,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="180" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>368</v>
       </c>
@@ -5483,7 +5483,7 @@
         <v>46024</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>8</v>
@@ -5492,7 +5492,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="181" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>370</v>
       </c>
@@ -5503,7 +5503,7 @@
         <v>46024</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>8</v>
@@ -5512,7 +5512,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="182" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>372</v>
       </c>
@@ -5523,7 +5523,7 @@
         <v>46024</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>8</v>
@@ -5592,7 +5592,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="186" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>381</v>
       </c>
@@ -5617,7 +5617,7 @@
         <v>383</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>500</v>
+        <v>465</v>
       </c>
       <c r="C187" s="3">
         <v>46024</v>
@@ -5657,7 +5657,7 @@
         <v>387</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>501</v>
+        <v>466</v>
       </c>
       <c r="C189" s="3">
         <v>46024</v>
@@ -5732,7 +5732,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="193" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>394</v>
       </c>
@@ -5752,7 +5752,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="194" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>396</v>
       </c>
@@ -5792,7 +5792,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="196" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>400</v>
       </c>
@@ -5832,7 +5832,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="198" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>404</v>
       </c>
@@ -5852,7 +5852,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="199" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>406</v>
       </c>
@@ -5872,7 +5872,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="200" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>408</v>
       </c>
@@ -5892,7 +5892,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="201" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>410</v>
       </c>
@@ -5912,7 +5912,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="202" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>413</v>
       </c>
@@ -5932,7 +5932,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="203" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>415</v>
       </c>
@@ -5992,7 +5992,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="206" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>422</v>
       </c>
@@ -6012,7 +6012,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="207" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>424</v>
       </c>
@@ -6023,7 +6023,7 @@
         <v>46024</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>426</v>
@@ -6032,7 +6032,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="208" spans="1:6" ht="216" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>427</v>
       </c>
@@ -6052,7 +6052,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="209" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>429</v>
       </c>
@@ -6072,7 +6072,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="210" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>431</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="211" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>434</v>
       </c>
@@ -6112,7 +6112,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="212" spans="1:6" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>436</v>
       </c>
@@ -6132,7 +6132,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="213" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>438</v>
       </c>
@@ -6152,7 +6152,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="214" spans="1:6" ht="216" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>440</v>
       </c>
@@ -6172,7 +6172,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="215" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>443</v>
       </c>
@@ -6232,7 +6232,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="218" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>449</v>
       </c>

--- a/Faculties/Natural Science/Postgrad Modules Natural Science.xlsx
+++ b/Faculties/Natural Science/Postgrad Modules Natural Science.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mwamb\OneDrive\Desktop\Team_6_repo\Team19\Faculties\Natural Science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09881E10-78C0-44E2-94C9-6677A295E75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F567E086-A037-418A-826A-1B2777668633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,15 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="509">
   <si>
-    <t>Module Code</t>
-  </si>
-  <si>
-    <t>Module Name</t>
-  </si>
-  <si>
-    <t>Year Level</t>
-  </si>
-  <si>
     <t>Programmes</t>
   </si>
   <si>
@@ -54,6 +45,693 @@
     <t>None</t>
   </si>
   <si>
+    <t>ASP703</t>
+  </si>
+  <si>
+    <t>General Astrophysics 703</t>
+  </si>
+  <si>
+    <t>ASP704</t>
+  </si>
+  <si>
+    <t>Computational Methods in Astronomy 704</t>
+  </si>
+  <si>
+    <t>ASP706</t>
+  </si>
+  <si>
+    <t>Astrophysical Physics Topics 706</t>
+  </si>
+  <si>
+    <t>ASP707</t>
+  </si>
+  <si>
+    <t>Geospace 707</t>
+  </si>
+  <si>
+    <t>ASP708</t>
+  </si>
+  <si>
+    <t>General Relativity 708</t>
+  </si>
+  <si>
+    <t>ASP709</t>
+  </si>
+  <si>
+    <t>Observational Techniques 709</t>
+  </si>
+  <si>
+    <t>BCB700</t>
+  </si>
+  <si>
+    <t>Research Project 700</t>
+  </si>
+  <si>
+    <t>BCB736</t>
+  </si>
+  <si>
+    <t>Biodiversity Information Management 736</t>
+  </si>
+  <si>
+    <t>BCB738</t>
+  </si>
+  <si>
+    <t>Marine Biology 738</t>
+  </si>
+  <si>
+    <t>BCB739</t>
+  </si>
+  <si>
+    <t>Herpetology 739</t>
+  </si>
+  <si>
+    <t>BCB743</t>
+  </si>
+  <si>
+    <t>Quantitative Ecology 743</t>
+  </si>
+  <si>
+    <t>BCB744</t>
+  </si>
+  <si>
+    <t>Biostatistics 744</t>
+  </si>
+  <si>
+    <t>BTY703</t>
+  </si>
+  <si>
+    <t>Research Project 703</t>
+  </si>
+  <si>
+    <t>BTY704</t>
+  </si>
+  <si>
+    <t>Advanced Plant Biotechnology 704</t>
+  </si>
+  <si>
+    <t>60% in GEO 3rd Yr</t>
+  </si>
+  <si>
+    <t>BTY709</t>
+  </si>
+  <si>
+    <t>Genomics 709</t>
+  </si>
+  <si>
+    <t>CHM703</t>
+  </si>
+  <si>
+    <t>Inorganic Chemistry 703</t>
+  </si>
+  <si>
+    <t>CHM704</t>
+  </si>
+  <si>
+    <t>Physical Chemistry 704</t>
+  </si>
+  <si>
+    <t>CHM705</t>
+  </si>
+  <si>
+    <t>Applied Chemistry 705</t>
+  </si>
+  <si>
+    <t>CHM707</t>
+  </si>
+  <si>
+    <t>Research Project 707</t>
+  </si>
+  <si>
+    <t>CHM708</t>
+  </si>
+  <si>
+    <t>Chemistry Advanced Specialist Topics 708</t>
+  </si>
+  <si>
+    <t>COS734</t>
+  </si>
+  <si>
+    <t>ICT4D</t>
+  </si>
+  <si>
+    <t>COS735</t>
+  </si>
+  <si>
+    <t>An Introduction to the Internet of Things 735</t>
+  </si>
+  <si>
+    <t>COS736</t>
+  </si>
+  <si>
+    <t>Big Data Engineering 736</t>
+  </si>
+  <si>
+    <t>COS737</t>
+  </si>
+  <si>
+    <t>COS738</t>
+  </si>
+  <si>
+    <t>COS739</t>
+  </si>
+  <si>
+    <t>COS740</t>
+  </si>
+  <si>
+    <t>COS743</t>
+  </si>
+  <si>
+    <t>EWP703</t>
+  </si>
+  <si>
+    <t>Groundwater Hydrology 703</t>
+  </si>
+  <si>
+    <t>EWP704</t>
+  </si>
+  <si>
+    <t>Surface Water Hydrology 704</t>
+  </si>
+  <si>
+    <t>EWP705</t>
+  </si>
+  <si>
+    <t>Research Project or Internship 705</t>
+  </si>
+  <si>
+    <t>EWP707</t>
+  </si>
+  <si>
+    <t>Anthropocene Rivers 707</t>
+  </si>
+  <si>
+    <t>MAM707</t>
+  </si>
+  <si>
+    <t>Ordinary Differential Equations 707</t>
+  </si>
+  <si>
+    <t>MAM709</t>
+  </si>
+  <si>
+    <t>Number Theory 709</t>
+  </si>
+  <si>
+    <t>MAM737</t>
+  </si>
+  <si>
+    <t>Topology 737</t>
+  </si>
+  <si>
+    <t>MAM738</t>
+  </si>
+  <si>
+    <t>Functions of a Complex Variable 738</t>
+  </si>
+  <si>
+    <t>MAM739</t>
+  </si>
+  <si>
+    <t>Group Theory 739</t>
+  </si>
+  <si>
+    <t>MAM747</t>
+  </si>
+  <si>
+    <t>Coding Theory 747</t>
+  </si>
+  <si>
+    <t>MAM748</t>
+  </si>
+  <si>
+    <t>Project 748</t>
+  </si>
+  <si>
+    <t>MAM757</t>
+  </si>
+  <si>
+    <t>Rings and Modules 757</t>
+  </si>
+  <si>
+    <t>MAM767</t>
+  </si>
+  <si>
+    <t>Functional Analysis 767</t>
+  </si>
+  <si>
+    <t>MAM777</t>
+  </si>
+  <si>
+    <t>Numerical Analysis 777</t>
+  </si>
+  <si>
+    <t>MBS704</t>
+  </si>
+  <si>
+    <t>Research Project 704</t>
+  </si>
+  <si>
+    <t>MBS705</t>
+  </si>
+  <si>
+    <t>Specialist Module in Anatomical Science 705</t>
+  </si>
+  <si>
+    <t>MBS707</t>
+  </si>
+  <si>
+    <t>Microbiology of Female Morbidity 707</t>
+  </si>
+  <si>
+    <t>MBS709</t>
+  </si>
+  <si>
+    <t>Microbiology of Female Morbidity 709</t>
+  </si>
+  <si>
+    <t>PHY709</t>
+  </si>
+  <si>
+    <t>Physics 709</t>
+  </si>
+  <si>
+    <t>POP703</t>
+  </si>
+  <si>
+    <t>Official Statistics 703</t>
+  </si>
+  <si>
+    <t>POP706</t>
+  </si>
+  <si>
+    <t>Survey Methods 706</t>
+  </si>
+  <si>
+    <t>POP707</t>
+  </si>
+  <si>
+    <t>Demographic Analysis 707</t>
+  </si>
+  <si>
+    <t>POP708</t>
+  </si>
+  <si>
+    <t>Gender Issues and Reproductive Health 708</t>
+  </si>
+  <si>
+    <t>POP707 or equiv</t>
+  </si>
+  <si>
+    <t>POP709</t>
+  </si>
+  <si>
+    <t>Social Demography 709</t>
+  </si>
+  <si>
+    <t>POP707 + Maths</t>
+  </si>
+  <si>
+    <t>STA705</t>
+  </si>
+  <si>
+    <t>Theoretical Statistics 705</t>
+  </si>
+  <si>
+    <t>STA733</t>
+  </si>
+  <si>
+    <t>Biostatistics 733</t>
+  </si>
+  <si>
+    <t>STA736</t>
+  </si>
+  <si>
+    <t>Statistical Genetics 736</t>
+  </si>
+  <si>
+    <t>STA737</t>
+  </si>
+  <si>
+    <t>Statistical Modelling 737</t>
+  </si>
+  <si>
+    <t>STA738</t>
+  </si>
+  <si>
+    <t>Applied Analytics 738</t>
+  </si>
+  <si>
+    <t>STA739</t>
+  </si>
+  <si>
+    <t>Introductory Multivariate Analysis 739</t>
+  </si>
+  <si>
+    <t>STA760</t>
+  </si>
+  <si>
+    <t>Data Mining I 760</t>
+  </si>
+  <si>
+    <t>STA790</t>
+  </si>
+  <si>
+    <t>Population Projections 790</t>
+  </si>
+  <si>
+    <t>WAT733</t>
+  </si>
+  <si>
+    <t>Spatial Analysis for IWRM 733</t>
+  </si>
+  <si>
+    <t>WAT734</t>
+  </si>
+  <si>
+    <t>Environmental Management and Water Regulations 734</t>
+  </si>
+  <si>
+    <t>WAT735</t>
+  </si>
+  <si>
+    <t>Water Quality Management 735</t>
+  </si>
+  <si>
+    <t>WAT736</t>
+  </si>
+  <si>
+    <t>Aquatic Ecosystems Management 736</t>
+  </si>
+  <si>
+    <t>WAT737</t>
+  </si>
+  <si>
+    <t>Environmental Education and Water Security 737</t>
+  </si>
+  <si>
+    <t>WAT738</t>
+  </si>
+  <si>
+    <t>Water Demand Management for Sustainable Dev 738</t>
+  </si>
+  <si>
+    <t>AIM803</t>
+  </si>
+  <si>
+    <t>COF835</t>
+  </si>
+  <si>
+    <t>Credit Derivatives 835</t>
+  </si>
+  <si>
+    <t>COF836</t>
+  </si>
+  <si>
+    <t>Linear Financial Models 836</t>
+  </si>
+  <si>
+    <t>NSS803/804</t>
+  </si>
+  <si>
+    <t>Nanoscience Research Project 803/804</t>
+  </si>
+  <si>
+    <t>NSS809</t>
+  </si>
+  <si>
+    <t>Central Concepts in Nanoscience 809</t>
+  </si>
+  <si>
+    <t>NSS833</t>
+  </si>
+  <si>
+    <t>PAR803/804</t>
+  </si>
+  <si>
+    <t>Mini Thesis 803/804</t>
+  </si>
+  <si>
+    <t>PHC803/804</t>
+  </si>
+  <si>
+    <t>Mini-Thesis in Clinical Pharmacy 803/804</t>
+  </si>
+  <si>
+    <t>BPharm</t>
+  </si>
+  <si>
+    <t>PHY830</t>
+  </si>
+  <si>
+    <t>Nuclear Physics 830</t>
+  </si>
+  <si>
+    <t>PHY840</t>
+  </si>
+  <si>
+    <t>Solid State Physics 840</t>
+  </si>
+  <si>
+    <t>PHY850</t>
+  </si>
+  <si>
+    <t>Physics Education 850</t>
+  </si>
+  <si>
+    <t>PHY860</t>
+  </si>
+  <si>
+    <t>Mathematical Methods of Physics 860</t>
+  </si>
+  <si>
+    <t>POP807</t>
+  </si>
+  <si>
+    <t>Demographic Analysis 807</t>
+  </si>
+  <si>
+    <t>POP809</t>
+  </si>
+  <si>
+    <t>Official Statistics 809</t>
+  </si>
+  <si>
+    <t>POP807 or equiv</t>
+  </si>
+  <si>
+    <t>POP848</t>
+  </si>
+  <si>
+    <t>Math Demography and Pop Modelling 848</t>
+  </si>
+  <si>
+    <t>POP807 + Maths</t>
+  </si>
+  <si>
+    <t>STA800</t>
+  </si>
+  <si>
+    <t>Data Mining II 800</t>
+  </si>
+  <si>
+    <t>STA803/804</t>
+  </si>
+  <si>
+    <t>Statistics Mini-Thesis 803/804</t>
+  </si>
+  <si>
+    <t>STA853 or equiv + SAS</t>
+  </si>
+  <si>
+    <t>STA830</t>
+  </si>
+  <si>
+    <t>Experimental Design 830</t>
+  </si>
+  <si>
+    <t>STA835</t>
+  </si>
+  <si>
+    <t>Biostatistics 835</t>
+  </si>
+  <si>
+    <t>STA837</t>
+  </si>
+  <si>
+    <t>Statistical Genetics 837</t>
+  </si>
+  <si>
+    <t>STA839</t>
+  </si>
+  <si>
+    <t>Industry Research Project 839</t>
+  </si>
+  <si>
+    <t>STA843</t>
+  </si>
+  <si>
+    <t>Multicriteria Decision Making 843</t>
+  </si>
+  <si>
+    <t>STA853</t>
+  </si>
+  <si>
+    <t>Matrix Methods 853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer Science 737  Artificial Intelligence </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer Science 738  Cybersecurity </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer Science 739  4IR Special Topics </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer Science 740  Cloud Computing </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer Science 743  Adv Immersive Tech </t>
+  </si>
+  <si>
+    <t>Mini-Thesis  Research Project  803</t>
+  </si>
+  <si>
+    <t>Foundations of Nanophysics  Non-Phys  833</t>
+  </si>
+  <si>
+    <t>BScHons Astrophysics 3793</t>
+  </si>
+  <si>
+    <t>BScHons Biotechnology 3707</t>
+  </si>
+  <si>
+    <t>BScHons Chemistry 3734</t>
+  </si>
+  <si>
+    <t>BScHons Statistical Science 3737, BScHons Computational Finance 3739</t>
+  </si>
+  <si>
+    <t>BScHons Mathematical Science 3736, BScHons Computational Finance 3739</t>
+  </si>
+  <si>
+    <t>BScHons Computational Finance 3739, BScHons Statistical Science 3737</t>
+  </si>
+  <si>
+    <t>BScHons Computer Science 3735</t>
+  </si>
+  <si>
+    <t>BScHons Computer Science 3735, BScHons Statistical Science 3737</t>
+  </si>
+  <si>
+    <t>BScHons Environment and Water Science 3780</t>
+  </si>
+  <si>
+    <t>BScHons Mathematical Science 3736</t>
+  </si>
+  <si>
+    <t>BScHons Mathematical Science 3736, BScHons Statistical Science 3737</t>
+  </si>
+  <si>
+    <t>BScHons Mathematical Science 3736, BScHons Computational Finance 3739, BScHons Computer Science 3735</t>
+  </si>
+  <si>
+    <t>BScHons Mathematical Science 3736, BScHons Computer Science 3735</t>
+  </si>
+  <si>
+    <t>BScHons Population Studies 3738</t>
+  </si>
+  <si>
+    <t>BScHons Population Studies 3738, BScHons Statistical Science 3737</t>
+  </si>
+  <si>
+    <t>BScHons Statistical Science 3737</t>
+  </si>
+  <si>
+    <t>BScHons Computational Finance 3739</t>
+  </si>
+  <si>
+    <t>BScHons Statistical Science 3737, BScHons Computer Science 3735</t>
+  </si>
+  <si>
+    <t>PGDip IWRM 3880</t>
+  </si>
+  <si>
+    <t>MSc Mathematical Science 3849</t>
+  </si>
+  <si>
+    <t>MSc Statistical Science 3838, MSc Computational Finance 3093</t>
+  </si>
+  <si>
+    <t>MSc Computational Finance 3093</t>
+  </si>
+  <si>
+    <t>MSc Computational Finance 3093, MSc Statistical Science 3838</t>
+  </si>
+  <si>
+    <t>MSc Nanoscience 3089</t>
+  </si>
+  <si>
+    <t>MSc Pharmacy Admin and Policy Regulation 3859</t>
+  </si>
+  <si>
+    <t>MSc Statistical Science 3838</t>
+  </si>
+  <si>
+    <t>MSc Statistical Sciences 3838</t>
+  </si>
+  <si>
+    <t>Module code</t>
+  </si>
+  <si>
+    <t>Module name</t>
+  </si>
+  <si>
+    <t>BScHons Applied Geology 3710</t>
+  </si>
+  <si>
+    <t>BScHons Biodiversity and Conservation Biology 3731</t>
+  </si>
+  <si>
+    <t>BScHons Astrophysics 3793, BScHons Physical Science 3714</t>
+  </si>
+  <si>
+    <t>BScHons Physical Science 3714</t>
+  </si>
+  <si>
+    <t>BScHons Physical Science 3714, BScHons Computer Science 3735</t>
+  </si>
+  <si>
+    <t>BScHons Biotechnology 3707, BScHons Medical Bioscience 3721</t>
+  </si>
+  <si>
+    <t>BScHons Medical Bioscience 3721</t>
+  </si>
+  <si>
+    <t>BScHons Population Studies 3738, BScHons Medical Bioscience 3721</t>
+  </si>
+  <si>
+    <t>PGDip Computer and Media Application 1627</t>
+  </si>
+  <si>
+    <t>MPhil Population Studies 3921, MSc Statistical Science 3838, MSc Computational Finance 3093</t>
+  </si>
+  <si>
+    <t>MPhil Population Studies 3921</t>
+  </si>
+  <si>
+    <t>MSc Statistical Science 3838, MSc Computational Finance 3093, MPhil Population Studies 3921</t>
+  </si>
+  <si>
+    <t>MSc Statistical Science 3838, MPhil Population Studies 3921</t>
+  </si>
+  <si>
+    <t>MSc Statistical Science 3838, MSc Medical Biosciences 3819, MPhil Population Studies 3921</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
     <t>APG721</t>
   </si>
   <si>
@@ -93,42 +771,6 @@
     <t>Topics in Physics 702</t>
   </si>
   <si>
-    <t>ASP703</t>
-  </si>
-  <si>
-    <t>General Astrophysics 703</t>
-  </si>
-  <si>
-    <t>ASP704</t>
-  </si>
-  <si>
-    <t>Computational Methods in Astronomy 704</t>
-  </si>
-  <si>
-    <t>ASP706</t>
-  </si>
-  <si>
-    <t>Astrophysical Physics Topics 706</t>
-  </si>
-  <si>
-    <t>ASP707</t>
-  </si>
-  <si>
-    <t>Geospace 707</t>
-  </si>
-  <si>
-    <t>ASP708</t>
-  </si>
-  <si>
-    <t>General Relativity 708</t>
-  </si>
-  <si>
-    <t>ASP709</t>
-  </si>
-  <si>
-    <t>Observational Techniques 709</t>
-  </si>
-  <si>
     <t>ASP710</t>
   </si>
   <si>
@@ -153,54 +795,18 @@
     <t>Electrodynamics 713</t>
   </si>
   <si>
-    <t>BCB700</t>
-  </si>
-  <si>
-    <t>Research Project 700</t>
-  </si>
-  <si>
     <t>BCB731</t>
   </si>
   <si>
     <t>Systematics and Evolution 731</t>
   </si>
   <si>
-    <t>BCB736</t>
-  </si>
-  <si>
-    <t>Biodiversity Information Management 736</t>
-  </si>
-  <si>
-    <t>BCB738</t>
-  </si>
-  <si>
-    <t>Marine Biology 738</t>
-  </si>
-  <si>
-    <t>BCB739</t>
-  </si>
-  <si>
-    <t>Herpetology 739</t>
-  </si>
-  <si>
     <t>BCB742</t>
   </si>
   <si>
     <t>Research Method 742</t>
   </si>
   <si>
-    <t>BCB743</t>
-  </si>
-  <si>
-    <t>Quantitative Ecology 743</t>
-  </si>
-  <si>
-    <t>BCB744</t>
-  </si>
-  <si>
-    <t>Biostatistics 744</t>
-  </si>
-  <si>
     <t>BTY701</t>
   </si>
   <si>
@@ -213,27 +819,6 @@
     <t>Literature Review 702</t>
   </si>
   <si>
-    <t>BTY703</t>
-  </si>
-  <si>
-    <t>Research Project 703</t>
-  </si>
-  <si>
-    <t>BTY704</t>
-  </si>
-  <si>
-    <t>Advanced Plant Biotechnology 704</t>
-  </si>
-  <si>
-    <t>60% in GEO 3rd Yr</t>
-  </si>
-  <si>
-    <t>BTY709</t>
-  </si>
-  <si>
-    <t>Genomics 709</t>
-  </si>
-  <si>
     <t>BTY710</t>
   </si>
   <si>
@@ -294,36 +879,6 @@
     <t>Organic Chemistry 702</t>
   </si>
   <si>
-    <t>CHM703</t>
-  </si>
-  <si>
-    <t>Inorganic Chemistry 703</t>
-  </si>
-  <si>
-    <t>CHM704</t>
-  </si>
-  <si>
-    <t>Physical Chemistry 704</t>
-  </si>
-  <si>
-    <t>CHM705</t>
-  </si>
-  <si>
-    <t>Applied Chemistry 705</t>
-  </si>
-  <si>
-    <t>CHM707</t>
-  </si>
-  <si>
-    <t>Research Project 707</t>
-  </si>
-  <si>
-    <t>CHM708</t>
-  </si>
-  <si>
-    <t>Chemistry Advanced Specialist Topics 708</t>
-  </si>
-  <si>
     <t>CMP716</t>
   </si>
   <si>
@@ -399,46 +954,19 @@
     <t>Project Implementation and Testing 732</t>
   </si>
   <si>
-    <t>COS734</t>
-  </si>
-  <si>
-    <t>ICT4D</t>
-  </si>
-  <si>
-    <t>COS735</t>
-  </si>
-  <si>
-    <t>An Introduction to the Internet of Things 735</t>
-  </si>
-  <si>
-    <t>COS736</t>
-  </si>
-  <si>
-    <t>Big Data Engineering 736</t>
-  </si>
-  <si>
-    <t>COS737</t>
-  </si>
-  <si>
-    <t>COS738</t>
-  </si>
-  <si>
-    <t>COS739</t>
-  </si>
-  <si>
-    <t>COS740</t>
-  </si>
-  <si>
     <t>COS741</t>
   </si>
   <si>
+    <t xml:space="preserve">Computer Science 741  Applied AI </t>
+  </si>
+  <si>
     <t>CSC311, CSC312</t>
   </si>
   <si>
     <t>COS742</t>
   </si>
   <si>
-    <t>COS743</t>
+    <t xml:space="preserve">Computer Science 742  Immersive Tech </t>
   </si>
   <si>
     <t>EWP701</t>
@@ -453,42 +981,6 @@
     <t>Advanced Geographical Information Systems 702</t>
   </si>
   <si>
-    <t>EWP703</t>
-  </si>
-  <si>
-    <t>Groundwater Hydrology 703</t>
-  </si>
-  <si>
-    <t>EWP704</t>
-  </si>
-  <si>
-    <t>Surface Water Hydrology 704</t>
-  </si>
-  <si>
-    <t>EWP705</t>
-  </si>
-  <si>
-    <t>Research Project or Internship 705</t>
-  </si>
-  <si>
-    <t>EWP707</t>
-  </si>
-  <si>
-    <t>Anthropocene Rivers 707</t>
-  </si>
-  <si>
-    <t>MAM707</t>
-  </si>
-  <si>
-    <t>Ordinary Differential Equations 707</t>
-  </si>
-  <si>
-    <t>MAM709</t>
-  </si>
-  <si>
-    <t>Number Theory 709</t>
-  </si>
-  <si>
     <t>MAM710</t>
   </si>
   <si>
@@ -525,54 +1017,6 @@
     <t>Category Theory and Order Theory 732</t>
   </si>
   <si>
-    <t>MAM737</t>
-  </si>
-  <si>
-    <t>Topology 737</t>
-  </si>
-  <si>
-    <t>MAM738</t>
-  </si>
-  <si>
-    <t>Functions of a Complex Variable 738</t>
-  </si>
-  <si>
-    <t>MAM739</t>
-  </si>
-  <si>
-    <t>Group Theory 739</t>
-  </si>
-  <si>
-    <t>MAM747</t>
-  </si>
-  <si>
-    <t>Coding Theory 747</t>
-  </si>
-  <si>
-    <t>MAM748</t>
-  </si>
-  <si>
-    <t>Project 748</t>
-  </si>
-  <si>
-    <t>MAM757</t>
-  </si>
-  <si>
-    <t>Rings and Modules 757</t>
-  </si>
-  <si>
-    <t>MAM767</t>
-  </si>
-  <si>
-    <t>Functional Analysis 767</t>
-  </si>
-  <si>
-    <t>MAM777</t>
-  </si>
-  <si>
-    <t>Numerical Analysis 777</t>
-  </si>
-  <si>
     <t>MBS701</t>
   </si>
   <si>
@@ -585,30 +1029,6 @@
     <t>Advanced Technique Studies 702</t>
   </si>
   <si>
-    <t>MBS704</t>
-  </si>
-  <si>
-    <t>Research Project 704</t>
-  </si>
-  <si>
-    <t>MBS705</t>
-  </si>
-  <si>
-    <t>Specialist Module in Anatomical Science 705</t>
-  </si>
-  <si>
-    <t>MBS707</t>
-  </si>
-  <si>
-    <t>Microbiology of Female Morbidity 707</t>
-  </si>
-  <si>
-    <t>MBS709</t>
-  </si>
-  <si>
-    <t>Microbiology of Female Morbidity 709</t>
-  </si>
-  <si>
     <t>MBS712</t>
   </si>
   <si>
@@ -639,12 +1059,6 @@
     <t>Nutrition in Health and Disease 716</t>
   </si>
   <si>
-    <t>PHY709</t>
-  </si>
-  <si>
-    <t>Physics 709</t>
-  </si>
-  <si>
     <t>PHY720</t>
   </si>
   <si>
@@ -687,51 +1101,18 @@
     <t>Advanced Analytical Techniques 726</t>
   </si>
   <si>
-    <t>POP703</t>
-  </si>
-  <si>
-    <t>Official Statistics 703</t>
-  </si>
-  <si>
-    <t>POP706</t>
-  </si>
-  <si>
-    <t>Survey Methods 706</t>
-  </si>
-  <si>
-    <t>POP707</t>
-  </si>
-  <si>
-    <t>Demographic Analysis 707</t>
-  </si>
-  <si>
-    <t>POP708</t>
-  </si>
-  <si>
-    <t>Gender Issues and Reproductive Health 708</t>
-  </si>
-  <si>
-    <t>POP707 or equiv</t>
-  </si>
-  <si>
-    <t>POP709</t>
-  </si>
-  <si>
-    <t>Social Demography 709</t>
-  </si>
-  <si>
     <t>POP710</t>
   </si>
   <si>
     <t>Mathematical Demography and Pop Modelling 710</t>
   </si>
   <si>
-    <t>POP707 + Maths</t>
-  </si>
-  <si>
     <t>POP761</t>
   </si>
   <si>
+    <t>Research Project  Population Studies  761</t>
+  </si>
+  <si>
     <t>STA501</t>
   </si>
   <si>
@@ -744,18 +1125,15 @@
     <t>Multivariate Analysis 701</t>
   </si>
   <si>
+    <t xml:space="preserve">STA331, STA332,  STA739 </t>
+  </si>
+  <si>
     <t>STA702</t>
   </si>
   <si>
     <t>Research Methodology 702</t>
   </si>
   <si>
-    <t>STA705</t>
-  </si>
-  <si>
-    <t>Theoretical Statistics 705</t>
-  </si>
-  <si>
     <t>STA331, STA332, MAT211</t>
   </si>
   <si>
@@ -768,57 +1146,15 @@
     <t>STA331, STA332 or equiv</t>
   </si>
   <si>
-    <t>STA733</t>
-  </si>
-  <si>
-    <t>Biostatistics 733</t>
-  </si>
-  <si>
-    <t>STA736</t>
-  </si>
-  <si>
-    <t>Statistical Genetics 736</t>
-  </si>
-  <si>
     <t>STA701, STA733, COF712</t>
   </si>
   <si>
-    <t>STA737</t>
-  </si>
-  <si>
-    <t>Statistical Modelling 737</t>
-  </si>
-  <si>
-    <t>STA738</t>
-  </si>
-  <si>
-    <t>Applied Analytics 738</t>
-  </si>
-  <si>
-    <t>STA739</t>
-  </si>
-  <si>
-    <t>Introductory Multivariate Analysis 739</t>
-  </si>
-  <si>
-    <t>STA760</t>
-  </si>
-  <si>
-    <t>Data Mining I 760</t>
-  </si>
-  <si>
     <t>STA761</t>
   </si>
   <si>
     <t>Honors Project 761</t>
   </si>
   <si>
-    <t>STA790</t>
-  </si>
-  <si>
-    <t>Population Projections 790</t>
-  </si>
-  <si>
     <t>WAT731</t>
   </si>
   <si>
@@ -831,45 +1167,6 @@
     <t>Water Resources Management 732</t>
   </si>
   <si>
-    <t>WAT733</t>
-  </si>
-  <si>
-    <t>Spatial Analysis for IWRM 733</t>
-  </si>
-  <si>
-    <t>WAT734</t>
-  </si>
-  <si>
-    <t>Environmental Management and Water Regulations 734</t>
-  </si>
-  <si>
-    <t>WAT735</t>
-  </si>
-  <si>
-    <t>Water Quality Management 735</t>
-  </si>
-  <si>
-    <t>WAT736</t>
-  </si>
-  <si>
-    <t>Aquatic Ecosystems Management 736</t>
-  </si>
-  <si>
-    <t>WAT737</t>
-  </si>
-  <si>
-    <t>Environmental Education and Water Security 737</t>
-  </si>
-  <si>
-    <t>WAT738</t>
-  </si>
-  <si>
-    <t>Water Demand Management for Sustainable Dev 738</t>
-  </si>
-  <si>
-    <t>AIM803</t>
-  </si>
-  <si>
     <t>AIM811</t>
   </si>
   <si>
@@ -993,30 +1290,6 @@
     <t>MAN781, MAN756 or equiv</t>
   </si>
   <si>
-    <t>COF835</t>
-  </si>
-  <si>
-    <t>Credit Derivatives 835</t>
-  </si>
-  <si>
-    <t>COF836</t>
-  </si>
-  <si>
-    <t>Linear Financial Models 836</t>
-  </si>
-  <si>
-    <t>NSS803/804</t>
-  </si>
-  <si>
-    <t>Nanoscience Research Project 803/804</t>
-  </si>
-  <si>
-    <t>NSS809</t>
-  </si>
-  <si>
-    <t>Central Concepts in Nanoscience 809</t>
-  </si>
-  <si>
     <t>NSS810</t>
   </si>
   <si>
@@ -1038,6 +1311,9 @@
     <t>NSS813</t>
   </si>
   <si>
+    <t>Foundations of Nanobiomedical Science  Non-Bio  813</t>
+  </si>
+  <si>
     <t>NSS821</t>
   </si>
   <si>
@@ -1059,6 +1335,9 @@
     <t>NSS823</t>
   </si>
   <si>
+    <t>Foundations of Nanochemistry  Non-Chem  823</t>
+  </si>
+  <si>
     <t>NSS831</t>
   </si>
   <si>
@@ -1074,15 +1353,6 @@
     <t>Experimental Techniques in Nanophysics 832</t>
   </si>
   <si>
-    <t>NSS833</t>
-  </si>
-  <si>
-    <t>PAR803/804</t>
-  </si>
-  <si>
-    <t>Mini Thesis 803/804</t>
-  </si>
-  <si>
     <t>PAR811</t>
   </si>
   <si>
@@ -1149,10 +1419,7 @@
     <t>Health Economics 821</t>
   </si>
   <si>
-    <t>PHC803/804</t>
-  </si>
-  <si>
-    <t>Mini-Thesis in Clinical Pharmacy 803/804</t>
+    <t>Master of Clinical Pharmacy 3852</t>
   </si>
   <si>
     <t>PHC811</t>
@@ -1161,9 +1428,6 @@
     <t>Intro to Clinical Pharmacy and Pharm Care 811</t>
   </si>
   <si>
-    <t>BPharm</t>
-  </si>
-  <si>
     <t>PHC812</t>
   </si>
   <si>
@@ -1179,6 +1443,9 @@
     <t>PHC815</t>
   </si>
   <si>
+    <t>Pharmaceutical Care – Adult Medicine  1  815</t>
+  </si>
+  <si>
     <t>PHC816</t>
   </si>
   <si>
@@ -1191,6 +1458,9 @@
     <t>PHC820</t>
   </si>
   <si>
+    <t>Pharmaceutical Care - Adult Medicine  2  820</t>
+  </si>
+  <si>
     <t>PHC821</t>
   </si>
   <si>
@@ -1215,40 +1485,7 @@
     <t>Quantum Mechanics 820</t>
   </si>
   <si>
-    <t>PHY830</t>
-  </si>
-  <si>
-    <t>Nuclear Physics 830</t>
-  </si>
-  <si>
-    <t>PHY840</t>
-  </si>
-  <si>
-    <t>Solid State Physics 840</t>
-  </si>
-  <si>
-    <t>PHY850</t>
-  </si>
-  <si>
-    <t>Physics Education 850</t>
-  </si>
-  <si>
-    <t>PHY860</t>
-  </si>
-  <si>
-    <t>Mathematical Methods of Physics 860</t>
-  </si>
-  <si>
-    <t>POP807</t>
-  </si>
-  <si>
-    <t>Demographic Analysis 807</t>
-  </si>
-  <si>
-    <t>POP809</t>
-  </si>
-  <si>
-    <t>Official Statistics 809</t>
+    <t>MSc Physical Science 3081</t>
   </si>
   <si>
     <t>POP811</t>
@@ -1263,9 +1500,6 @@
     <t>Population Projections 812</t>
   </si>
   <si>
-    <t>POP807 or equiv</t>
-  </si>
-  <si>
     <t>POP813</t>
   </si>
   <si>
@@ -1284,21 +1518,6 @@
     <t>Gender Issues and Reproductive Health 815</t>
   </si>
   <si>
-    <t>POP848</t>
-  </si>
-  <si>
-    <t>Math Demography and Pop Modelling 848</t>
-  </si>
-  <si>
-    <t>POP807 + Maths</t>
-  </si>
-  <si>
-    <t>STA800</t>
-  </si>
-  <si>
-    <t>Data Mining II 800</t>
-  </si>
-  <si>
     <t>STA801/802</t>
   </si>
   <si>
@@ -1308,12 +1527,6 @@
     <t>STA810 or equivalent</t>
   </si>
   <si>
-    <t>STA803/804</t>
-  </si>
-  <si>
-    <t>Statistics Mini-Thesis 803/804</t>
-  </si>
-  <si>
     <t>STA810</t>
   </si>
   <si>
@@ -1326,33 +1539,6 @@
     <t>Multivariate Analysis 829</t>
   </si>
   <si>
-    <t>STA853 or equiv + SAS</t>
-  </si>
-  <si>
-    <t>STA830</t>
-  </si>
-  <si>
-    <t>Experimental Design 830</t>
-  </si>
-  <si>
-    <t>STA835</t>
-  </si>
-  <si>
-    <t>Biostatistics 835</t>
-  </si>
-  <si>
-    <t>STA837</t>
-  </si>
-  <si>
-    <t>Statistical Genetics 837</t>
-  </si>
-  <si>
-    <t>STA839</t>
-  </si>
-  <si>
-    <t>Industry Research Project 839</t>
-  </si>
-  <si>
     <t>STA810 + 3 electives</t>
   </si>
   <si>
@@ -1366,192 +1552,6 @@
   </si>
   <si>
     <t>Contemporary Business Analysis 842</t>
-  </si>
-  <si>
-    <t>STA843</t>
-  </si>
-  <si>
-    <t>Multicriteria Decision Making 843</t>
-  </si>
-  <si>
-    <t>STA853</t>
-  </si>
-  <si>
-    <t>Matrix Methods 853</t>
-  </si>
-  <si>
-    <t>Master of Clinical Pharmacy 3852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer Science 737  Artificial Intelligence </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer Science 738  Cybersecurity </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer Science 739  4IR Special Topics </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer Science 740  Cloud Computing </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer Science 741  Applied AI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer Science 742  Immersive Tech </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer Science 743  Adv Immersive Tech </t>
-  </si>
-  <si>
-    <t>Research Project  Population Studies  761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STA331, STA332,  STA739 </t>
-  </si>
-  <si>
-    <t>Mini-Thesis  Research Project  803</t>
-  </si>
-  <si>
-    <t>Foundations of Nanobiomedical Science  Non-Bio  813</t>
-  </si>
-  <si>
-    <t>Foundations of Nanochemistry  Non-Chem  823</t>
-  </si>
-  <si>
-    <t>Foundations of Nanophysics  Non-Phys  833</t>
-  </si>
-  <si>
-    <t>Pharmaceutical Care – Adult Medicine  1  815</t>
-  </si>
-  <si>
-    <t>Pharmaceutical Care - Adult Medicine  2  820</t>
-  </si>
-  <si>
-    <t>BScHons Applied Geology 3710</t>
-  </si>
-  <si>
-    <t>BScHons Astrophysics 3793</t>
-  </si>
-  <si>
-    <t>BScHons Astrophysics 3793, BScHons Physical Science 3714</t>
-  </si>
-  <si>
-    <t>BScHons Biodiversity and Conservation Biology 3731</t>
-  </si>
-  <si>
-    <t>BScHons Biotechnology 3707</t>
-  </si>
-  <si>
-    <t>BScHons Biotechnology 3707, BScHons Medical Bioscience 3721</t>
-  </si>
-  <si>
-    <t>BScHons Chemistry 3734</t>
-  </si>
-  <si>
-    <t>PGDip Computer and Media Application 1627</t>
-  </si>
-  <si>
-    <t>BScHons Statistical Science 3737, BScHons Computational Finance 3739</t>
-  </si>
-  <si>
-    <t>BScHons Mathematical Science 3736, BScHons Computational Finance 3739</t>
-  </si>
-  <si>
-    <t>BScHons Computational Finance 3739, BScHons Statistical Science 3737</t>
-  </si>
-  <si>
-    <t>BScHons Computer Science 3735</t>
-  </si>
-  <si>
-    <t>BScHons Computer Science 3735, BScHons Statistical Science 3737</t>
-  </si>
-  <si>
-    <t>BScHons Environment and Water Science 3780</t>
-  </si>
-  <si>
-    <t>BScHons Mathematical Science 3736</t>
-  </si>
-  <si>
-    <t>BScHons Mathematical Science 3736, BScHons Statistical Science 3737</t>
-  </si>
-  <si>
-    <t>BScHons Mathematical Science 3736, BScHons Computational Finance 3739, BScHons Computer Science 3735</t>
-  </si>
-  <si>
-    <t>BScHons Mathematical Science 3736, BScHons Computer Science 3735</t>
-  </si>
-  <si>
-    <t>BScHons Medical Bioscience 3721</t>
-  </si>
-  <si>
-    <t>BScHons Physical Science 3714</t>
-  </si>
-  <si>
-    <t>BScHons Physical Science 3714, BScHons Computer Science 3735</t>
-  </si>
-  <si>
-    <t>BScHons Population Studies 3738</t>
-  </si>
-  <si>
-    <t>BScHons Population Studies 3738, BScHons Statistical Science 3737</t>
-  </si>
-  <si>
-    <t>BScHons Population Studies 3738, BScHons Medical Bioscience 3721</t>
-  </si>
-  <si>
-    <t>BScHons Statistical Science 3737</t>
-  </si>
-  <si>
-    <t>BScHons Computational Finance 3739</t>
-  </si>
-  <si>
-    <t>BScHons Statistical Science 3737, BScHons Computer Science 3735</t>
-  </si>
-  <si>
-    <t>PGDip IWRM 3880</t>
-  </si>
-  <si>
-    <t>MSc Mathematical Science 3849</t>
-  </si>
-  <si>
-    <t>MSc Statistical Science 3838, MSc Computational Finance 3093</t>
-  </si>
-  <si>
-    <t>MSc Computational Finance 3093</t>
-  </si>
-  <si>
-    <t>MPhil Population Studies 3921, MSc Statistical Science 3838, MSc Computational Finance 3093</t>
-  </si>
-  <si>
-    <t>MSc Computational Finance 3093, MSc Statistical Science 3838</t>
-  </si>
-  <si>
-    <t>MSc Nanoscience 3089</t>
-  </si>
-  <si>
-    <t>MSc Pharmacy Admin and Policy Regulation 3859</t>
-  </si>
-  <si>
-    <t>MSc Physical Science 3081</t>
-  </si>
-  <si>
-    <t>MPhil Population Studies 3921</t>
-  </si>
-  <si>
-    <t>MSc Statistical Science 3838</t>
-  </si>
-  <si>
-    <t>MSc Statistical Science 3838, MSc Computational Finance 3093, MPhil Population Studies 3921</t>
-  </si>
-  <si>
-    <t>MSc Statistical Science 3838, MPhil Population Studies 3921</t>
-  </si>
-  <si>
-    <t>MSc Statistical Science 3838, MSc Medical Biosciences 3819, MPhil Population Studies 3921</t>
-  </si>
-  <si>
-    <t>MSc Statistical Sciences 3838</t>
   </si>
 </sst>
 </file>
@@ -1595,7 +1595,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1603,9 +1603,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1889,4367 +1893,4368 @@
   <dimension ref="A1:F218"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="3" max="3" width="8.88671875" style="5"/>
     <col min="4" max="4" width="23.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="C2" s="4">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>467</v>
+        <v>220</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>235</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1">
+        <v>236</v>
+      </c>
+      <c r="C3" s="4">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>467</v>
+        <v>220</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>237</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1">
+        <v>238</v>
+      </c>
+      <c r="C4" s="4">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>467</v>
+        <v>220</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>239</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1">
+        <v>240</v>
+      </c>
+      <c r="C5" s="4">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>467</v>
+        <v>220</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>241</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>16</v>
+        <v>242</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1">
+        <v>243</v>
+      </c>
+      <c r="C6" s="4">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>467</v>
+        <v>220</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>244</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="1">
+        <v>245</v>
+      </c>
+      <c r="C7" s="4">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>468</v>
+        <v>191</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="1">
+        <v>247</v>
+      </c>
+      <c r="C8" s="4">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>468</v>
+        <v>191</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="1">
+        <v>7</v>
+      </c>
+      <c r="C9" s="4">
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>469</v>
+        <v>222</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="1">
+        <v>9</v>
+      </c>
+      <c r="C10" s="4">
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>468</v>
+        <v>191</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="1">
+        <v>11</v>
+      </c>
+      <c r="C11" s="4">
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>468</v>
+        <v>191</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="1">
+        <v>13</v>
+      </c>
+      <c r="C12" s="4">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>468</v>
+        <v>191</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="1">
+        <v>15</v>
+      </c>
+      <c r="C13" s="4">
         <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>468</v>
+        <v>191</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="1">
+        <v>17</v>
+      </c>
+      <c r="C14" s="4">
         <v>1</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>468</v>
+        <v>191</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>248</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="1">
+        <v>249</v>
+      </c>
+      <c r="C15" s="4">
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>468</v>
+        <v>191</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>250</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="1">
+        <v>251</v>
+      </c>
+      <c r="C16" s="4">
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>468</v>
+        <v>191</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>38</v>
+        <v>252</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="1">
+        <v>253</v>
+      </c>
+      <c r="C17" s="4">
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>469</v>
+        <v>222</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>40</v>
+        <v>254</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="1">
+        <v>255</v>
+      </c>
+      <c r="C18" s="4">
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>468</v>
+        <v>191</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="1">
+        <v>19</v>
+      </c>
+      <c r="C19" s="4">
         <v>1</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>470</v>
+        <v>221</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>44</v>
+        <v>256</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="1">
+        <v>257</v>
+      </c>
+      <c r="C20" s="4">
         <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>470</v>
+        <v>221</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="1">
+        <v>21</v>
+      </c>
+      <c r="C21" s="4">
         <v>1</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>470</v>
+        <v>221</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" s="1">
+        <v>23</v>
+      </c>
+      <c r="C22" s="4">
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>470</v>
+        <v>221</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="1">
+        <v>25</v>
+      </c>
+      <c r="C23" s="4">
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>470</v>
+        <v>221</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>52</v>
+        <v>258</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="1">
+        <v>259</v>
+      </c>
+      <c r="C24" s="4">
         <v>1</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>470</v>
+        <v>221</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" s="1">
+        <v>27</v>
+      </c>
+      <c r="C25" s="4">
         <v>1</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>470</v>
+        <v>221</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="1">
+        <v>29</v>
+      </c>
+      <c r="C26" s="4">
         <v>1</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>470</v>
+        <v>221</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>58</v>
+        <v>260</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27" s="1">
+        <v>261</v>
+      </c>
+      <c r="C27" s="4">
         <v>1</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>471</v>
+        <v>192</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>60</v>
+        <v>262</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="1">
+        <v>263</v>
+      </c>
+      <c r="C28" s="4">
         <v>1</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>471</v>
+        <v>192</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C29" s="1">
+        <v>31</v>
+      </c>
+      <c r="C29" s="4">
         <v>1</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>471</v>
+        <v>192</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" s="1">
+        <v>33</v>
+      </c>
+      <c r="C30" s="4">
         <v>1</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>471</v>
+        <v>192</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C31" s="1">
+        <v>36</v>
+      </c>
+      <c r="C31" s="4">
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>471</v>
+        <v>192</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>69</v>
+        <v>264</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" s="1">
+        <v>265</v>
+      </c>
+      <c r="C32" s="4">
         <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>471</v>
+        <v>192</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>71</v>
+        <v>266</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" s="1">
+        <v>267</v>
+      </c>
+      <c r="C33" s="4">
         <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>471</v>
+        <v>192</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>73</v>
+        <v>268</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C34" s="1">
+        <v>269</v>
+      </c>
+      <c r="C34" s="4">
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>472</v>
+        <v>225</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>75</v>
+        <v>270</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C35" s="1">
+        <v>271</v>
+      </c>
+      <c r="C35" s="4">
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>471</v>
+        <v>192</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>77</v>
+        <v>272</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C36" s="1">
+        <v>273</v>
+      </c>
+      <c r="C36" s="4">
         <v>1</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>471</v>
+        <v>192</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>79</v>
+        <v>274</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C37" s="1">
+        <v>275</v>
+      </c>
+      <c r="C37" s="4">
         <v>1</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>471</v>
+        <v>192</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>81</v>
+        <v>276</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C38" s="1">
+        <v>277</v>
+      </c>
+      <c r="C38" s="4">
         <v>1</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>471</v>
+        <v>192</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>83</v>
+        <v>278</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C39" s="1">
+        <v>279</v>
+      </c>
+      <c r="C39" s="4">
         <v>1</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>471</v>
+        <v>192</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>85</v>
+        <v>280</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C40" s="1">
+        <v>281</v>
+      </c>
+      <c r="C40" s="4">
         <v>1</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>473</v>
+        <v>193</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>87</v>
+        <v>282</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" s="1">
+        <v>283</v>
+      </c>
+      <c r="C41" s="4">
         <v>1</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>473</v>
+        <v>193</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C42" s="1">
+        <v>38</v>
+      </c>
+      <c r="C42" s="4">
         <v>1</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>473</v>
+        <v>193</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C43" s="1">
+        <v>40</v>
+      </c>
+      <c r="C43" s="4">
         <v>1</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>473</v>
+        <v>193</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C44" s="1">
+        <v>42</v>
+      </c>
+      <c r="C44" s="4">
         <v>1</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>473</v>
+        <v>193</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C45" s="1">
+        <v>44</v>
+      </c>
+      <c r="C45" s="4">
         <v>1</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>473</v>
+        <v>193</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C46" s="1">
+        <v>46</v>
+      </c>
+      <c r="C46" s="4">
         <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>473</v>
+        <v>193</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>99</v>
+        <v>284</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C47" s="3">
-        <v>46024</v>
+        <v>285</v>
+      </c>
+      <c r="C47" s="4">
+        <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>474</v>
+        <v>228</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>101</v>
+        <v>286</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>102</v>
+        <v>287</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C48" s="1">
+        <v>288</v>
+      </c>
+      <c r="C48" s="4">
         <v>1</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>475</v>
+        <v>194</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>104</v>
+        <v>289</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>105</v>
+        <v>290</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C49" s="1">
+        <v>291</v>
+      </c>
+      <c r="C49" s="4">
         <v>1</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>475</v>
+        <v>194</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>107</v>
+        <v>292</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>108</v>
+        <v>293</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C50" s="1">
+        <v>294</v>
+      </c>
+      <c r="C50" s="4">
         <v>1</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>475</v>
+        <v>194</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>110</v>
+        <v>295</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>111</v>
+        <v>296</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C51" s="1">
+        <v>297</v>
+      </c>
+      <c r="C51" s="4">
         <v>1</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>476</v>
+        <v>195</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>113</v>
+        <v>298</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C52" s="1">
+        <v>299</v>
+      </c>
+      <c r="C52" s="4">
         <v>1</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>476</v>
+        <v>195</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>115</v>
+        <v>300</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C53" s="1">
+        <v>301</v>
+      </c>
+      <c r="C53" s="4">
         <v>1</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>477</v>
+        <v>196</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>110</v>
+        <v>295</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>117</v>
+        <v>302</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C54" s="1">
+        <v>303</v>
+      </c>
+      <c r="C54" s="4">
         <v>1</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>478</v>
+        <v>197</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>119</v>
+        <v>304</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>120</v>
+        <v>305</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C55" s="1">
+        <v>306</v>
+      </c>
+      <c r="C55" s="4">
         <v>1</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>478</v>
+        <v>197</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>122</v>
+        <v>307</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C56" s="1">
+        <v>308</v>
+      </c>
+      <c r="C56" s="4">
         <v>1</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>478</v>
+        <v>197</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>124</v>
+        <v>47</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C57" s="1">
+        <v>48</v>
+      </c>
+      <c r="C57" s="4">
         <v>1</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>478</v>
+        <v>197</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>126</v>
+        <v>49</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C58" s="1">
+        <v>50</v>
+      </c>
+      <c r="C58" s="4">
         <v>1</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>478</v>
+        <v>197</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>128</v>
+        <v>51</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C59" s="1">
+        <v>52</v>
+      </c>
+      <c r="C59" s="4">
         <v>1</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>479</v>
+        <v>198</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>130</v>
+        <v>53</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="C60" s="1">
+        <v>184</v>
+      </c>
+      <c r="C60" s="4">
         <v>1</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>479</v>
+        <v>198</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="C61" s="1">
+        <v>185</v>
+      </c>
+      <c r="C61" s="4">
         <v>1</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>478</v>
+        <v>197</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>132</v>
+        <v>55</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="C62" s="1">
+        <v>186</v>
+      </c>
+      <c r="C62" s="4">
         <v>1</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>478</v>
+        <v>197</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="C63" s="1">
+        <v>187</v>
+      </c>
+      <c r="C63" s="4">
         <v>1</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>478</v>
+        <v>197</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>134</v>
+        <v>309</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="C64" s="1">
+        <v>310</v>
+      </c>
+      <c r="C64" s="4">
         <v>1</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>478</v>
+        <v>197</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>135</v>
+        <v>311</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>136</v>
+        <v>312</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="C65" s="1">
+        <v>313</v>
+      </c>
+      <c r="C65" s="4">
         <v>1</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>478</v>
+        <v>197</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>137</v>
+        <v>57</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="C66" s="1">
+        <v>188</v>
+      </c>
+      <c r="C66" s="4">
         <v>1</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>478</v>
+        <v>197</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>138</v>
+        <v>314</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C67" s="1">
+        <v>315</v>
+      </c>
+      <c r="C67" s="4">
         <v>1</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>480</v>
+        <v>199</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>140</v>
+        <v>316</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C68" s="1">
+        <v>317</v>
+      </c>
+      <c r="C68" s="4">
         <v>1</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>480</v>
+        <v>199</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C69" s="1">
+        <v>59</v>
+      </c>
+      <c r="C69" s="4">
         <v>1</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>480</v>
+        <v>199</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C70" s="1">
+        <v>61</v>
+      </c>
+      <c r="C70" s="4">
         <v>1</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>480</v>
+        <v>199</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>146</v>
+        <v>62</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C71" s="1">
+        <v>63</v>
+      </c>
+      <c r="C71" s="4">
         <v>1</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>480</v>
+        <v>199</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>148</v>
+        <v>64</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C72" s="1">
+        <v>65</v>
+      </c>
+      <c r="C72" s="4">
         <v>1</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>480</v>
+        <v>199</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>150</v>
+        <v>66</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C73" s="1">
+        <v>67</v>
+      </c>
+      <c r="C73" s="4">
         <v>1</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>481</v>
+        <v>200</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>152</v>
+        <v>68</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C74" s="1">
+        <v>69</v>
+      </c>
+      <c r="C74" s="4">
         <v>1</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>481</v>
+        <v>200</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>154</v>
+        <v>318</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C75" s="1">
+        <v>319</v>
+      </c>
+      <c r="C75" s="4">
         <v>1</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>482</v>
+        <v>201</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>156</v>
+        <v>320</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C76" s="1">
+        <v>321</v>
+      </c>
+      <c r="C76" s="4">
         <v>1</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>481</v>
+        <v>200</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>158</v>
+        <v>322</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C77" s="1">
+        <v>323</v>
+      </c>
+      <c r="C77" s="4">
         <v>1</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>481</v>
+        <v>200</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>160</v>
+        <v>324</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C78" s="1">
+        <v>325</v>
+      </c>
+      <c r="C78" s="4">
         <v>1</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>483</v>
+        <v>202</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>162</v>
+        <v>326</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C79" s="1">
+        <v>327</v>
+      </c>
+      <c r="C79" s="4">
         <v>1</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>481</v>
+        <v>200</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C80" s="1">
+        <v>329</v>
+      </c>
+      <c r="C80" s="4">
         <v>1</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>481</v>
+        <v>200</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>166</v>
+        <v>70</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C81" s="1">
+        <v>71</v>
+      </c>
+      <c r="C81" s="4">
         <v>1</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>481</v>
+        <v>200</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>168</v>
+        <v>72</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C82" s="1">
+        <v>73</v>
+      </c>
+      <c r="C82" s="4">
         <v>1</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>481</v>
+        <v>200</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>170</v>
+        <v>74</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C83" s="1">
+        <v>75</v>
+      </c>
+      <c r="C83" s="4">
         <v>1</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>481</v>
+        <v>200</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>172</v>
+        <v>76</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C84" s="1">
+        <v>77</v>
+      </c>
+      <c r="C84" s="4">
         <v>1</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>484</v>
+        <v>203</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C85" s="1">
+        <v>79</v>
+      </c>
+      <c r="C85" s="4">
         <v>1</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>476</v>
+        <v>195</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>176</v>
+        <v>80</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C86" s="1">
+        <v>81</v>
+      </c>
+      <c r="C86" s="4">
         <v>1</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>481</v>
+        <v>200</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C87" s="1">
+        <v>83</v>
+      </c>
+      <c r="C87" s="4">
         <v>1</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>481</v>
+        <v>200</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C88" s="1">
+        <v>85</v>
+      </c>
+      <c r="C88" s="4">
         <v>1</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>481</v>
+        <v>200</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>182</v>
+        <v>330</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C89" s="1">
+        <v>331</v>
+      </c>
+      <c r="C89" s="4">
         <v>1</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>485</v>
+        <v>226</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>184</v>
+        <v>332</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C90" s="1">
+        <v>333</v>
+      </c>
+      <c r="C90" s="4">
         <v>1</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>485</v>
+        <v>226</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>186</v>
+        <v>86</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C91" s="1">
+        <v>87</v>
+      </c>
+      <c r="C91" s="4">
         <v>1</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>485</v>
+        <v>226</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>188</v>
+        <v>88</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C92" s="1">
+        <v>89</v>
+      </c>
+      <c r="C92" s="4">
         <v>1</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>485</v>
+        <v>226</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C93" s="1">
+        <v>91</v>
+      </c>
+      <c r="C93" s="4">
         <v>1</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>485</v>
+        <v>226</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>192</v>
+        <v>92</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C94" s="1">
+        <v>93</v>
+      </c>
+      <c r="C94" s="4">
         <v>1</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>485</v>
+        <v>226</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>194</v>
+        <v>334</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C95" s="1">
+        <v>335</v>
+      </c>
+      <c r="C95" s="4">
         <v>1</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>485</v>
+        <v>226</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>196</v>
+        <v>336</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C96" s="1">
+        <v>337</v>
+      </c>
+      <c r="C96" s="4">
         <v>1</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>485</v>
+        <v>226</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>198</v>
+        <v>338</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C97" s="1">
+        <v>339</v>
+      </c>
+      <c r="C97" s="4">
         <v>1</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>485</v>
+        <v>226</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>200</v>
+        <v>340</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C98" s="1">
+        <v>341</v>
+      </c>
+      <c r="C98" s="4">
         <v>1</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>485</v>
+        <v>226</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>202</v>
+        <v>342</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="C99" s="1">
+        <v>343</v>
+      </c>
+      <c r="C99" s="4">
         <v>1</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>485</v>
+        <v>226</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>204</v>
+        <v>94</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C100" s="1">
+        <v>95</v>
+      </c>
+      <c r="C100" s="4">
         <v>1</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>486</v>
+        <v>223</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>206</v>
+        <v>344</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C101" s="1">
+        <v>345</v>
+      </c>
+      <c r="C101" s="4">
         <v>1</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>487</v>
+        <v>224</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>208</v>
+        <v>346</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C102" s="1">
+        <v>347</v>
+      </c>
+      <c r="C102" s="4">
         <v>1</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>486</v>
+        <v>223</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>210</v>
+        <v>348</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C103" s="1">
+        <v>349</v>
+      </c>
+      <c r="C103" s="4">
         <v>1</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>486</v>
+        <v>223</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>212</v>
+        <v>350</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="C104" s="1">
+        <v>351</v>
+      </c>
+      <c r="C104" s="4">
         <v>1</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>486</v>
+        <v>223</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>206</v>
+        <v>344</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>214</v>
+        <v>352</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C105" s="1">
+        <v>353</v>
+      </c>
+      <c r="C105" s="4">
         <v>1</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>486</v>
+        <v>223</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>216</v>
+        <v>354</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C106" s="1">
+        <v>355</v>
+      </c>
+      <c r="C106" s="4">
         <v>1</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>486</v>
+        <v>223</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>214</v>
+        <v>352</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>218</v>
+        <v>356</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="C107" s="1">
+        <v>357</v>
+      </c>
+      <c r="C107" s="4">
         <v>1</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>487</v>
+        <v>224</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>214</v>
+        <v>352</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>220</v>
+        <v>96</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C108" s="1">
+        <v>97</v>
+      </c>
+      <c r="C108" s="4">
         <v>1</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>488</v>
+        <v>204</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>222</v>
+        <v>98</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="C109" s="1">
+        <v>99</v>
+      </c>
+      <c r="C109" s="4">
         <v>1</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>489</v>
+        <v>205</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>224</v>
+        <v>100</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="C110" s="1">
+        <v>101</v>
+      </c>
+      <c r="C110" s="4">
         <v>1</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>489</v>
+        <v>205</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>226</v>
+        <v>102</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="C111" s="1">
+        <v>103</v>
+      </c>
+      <c r="C111" s="4">
         <v>1</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>488</v>
+        <v>204</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>228</v>
+        <v>104</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>229</v>
+        <v>105</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C112" s="1">
+        <v>106</v>
+      </c>
+      <c r="C112" s="4">
         <v>1</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>488</v>
+        <v>204</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>228</v>
+        <v>104</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>231</v>
+        <v>358</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C113" s="1">
+        <v>359</v>
+      </c>
+      <c r="C113" s="4">
         <v>1</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>489</v>
+        <v>205</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>233</v>
+        <v>107</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>234</v>
+        <v>360</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="C114" s="1">
+        <v>361</v>
+      </c>
+      <c r="C114" s="4">
         <v>1</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>488</v>
+        <v>204</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>235</v>
+        <v>362</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="C115" s="1">
+        <v>363</v>
+      </c>
+      <c r="C115" s="4">
         <v>1</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>490</v>
+        <v>227</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>237</v>
+        <v>364</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="C116" s="1">
+        <v>365</v>
+      </c>
+      <c r="C116" s="4">
         <v>1</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>491</v>
+        <v>206</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>460</v>
+        <v>366</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>239</v>
+        <v>367</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C117" s="1">
+        <v>368</v>
+      </c>
+      <c r="C117" s="4">
         <v>1</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>492</v>
+        <v>207</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>235</v>
+        <v>362</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>241</v>
+        <v>108</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C118" s="1">
+        <v>109</v>
+      </c>
+      <c r="C118" s="4">
         <v>1</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>475</v>
+        <v>194</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>243</v>
+        <v>369</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>244</v>
+        <v>370</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C119" s="1">
+        <v>371</v>
+      </c>
+      <c r="C119" s="4">
         <v>1</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>491</v>
+        <v>206</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>246</v>
+        <v>372</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>247</v>
+        <v>110</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C120" s="1">
+        <v>111</v>
+      </c>
+      <c r="C120" s="4">
         <v>1</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>489</v>
+        <v>205</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>246</v>
+        <v>372</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>249</v>
+        <v>112</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="C121" s="1">
+        <v>113</v>
+      </c>
+      <c r="C121" s="4">
         <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>491</v>
+        <v>206</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>251</v>
+        <v>373</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>252</v>
+        <v>114</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C122" s="1">
+        <v>115</v>
+      </c>
+      <c r="C122" s="4">
         <v>1</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>491</v>
+        <v>206</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>254</v>
+        <v>116</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C123" s="1">
+        <v>117</v>
+      </c>
+      <c r="C123" s="4">
         <v>1</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>491</v>
+        <v>206</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>256</v>
+        <v>118</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C124" s="1">
+        <v>119</v>
+      </c>
+      <c r="C124" s="4">
         <v>1</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>491</v>
+        <v>206</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>258</v>
+        <v>120</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C125" s="1">
+        <v>121</v>
+      </c>
+      <c r="C125" s="4">
         <v>1</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>493</v>
+        <v>208</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>246</v>
+        <v>372</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>260</v>
+        <v>374</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C126" s="1">
+        <v>375</v>
+      </c>
+      <c r="C126" s="4">
         <v>1</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>475</v>
+        <v>194</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>262</v>
+        <v>122</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="C127" s="1">
+        <v>123</v>
+      </c>
+      <c r="C127" s="4">
         <v>1</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>489</v>
+        <v>205</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>228</v>
+        <v>104</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>264</v>
+        <v>376</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="C128" s="1">
+        <v>377</v>
+      </c>
+      <c r="C128" s="4">
         <v>1</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>494</v>
+        <v>209</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>266</v>
+        <v>378</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="C129" s="1">
+        <v>379</v>
+      </c>
+      <c r="C129" s="4">
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>494</v>
+        <v>209</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>268</v>
+        <v>124</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C130" s="1">
+        <v>125</v>
+      </c>
+      <c r="C130" s="4">
         <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>494</v>
+        <v>209</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>270</v>
+        <v>126</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C131" s="1">
+        <v>127</v>
+      </c>
+      <c r="C131" s="4">
         <v>1</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>494</v>
+        <v>209</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>272</v>
+        <v>128</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="C132" s="1">
+        <v>129</v>
+      </c>
+      <c r="C132" s="4">
         <v>1</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>494</v>
+        <v>209</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>274</v>
+        <v>130</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C133" s="1">
+        <v>131</v>
+      </c>
+      <c r="C133" s="4">
         <v>1</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>494</v>
+        <v>209</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>276</v>
+        <v>132</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="C134" s="1">
+        <v>133</v>
+      </c>
+      <c r="C134" s="4">
         <v>1</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>494</v>
+        <v>209</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>278</v>
+        <v>134</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C135" s="1">
+        <v>135</v>
+      </c>
+      <c r="C135" s="4">
         <v>1</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>494</v>
+        <v>209</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>280</v>
+        <v>136</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="C136" s="1">
+        <v>189</v>
+      </c>
+      <c r="C136" s="4">
         <v>1</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>495</v>
+        <v>210</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>281</v>
+        <v>380</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C137" s="3">
-        <v>46024</v>
+        <v>381</v>
+      </c>
+      <c r="C137" s="4">
+        <v>2</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>495</v>
+        <v>210</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>283</v>
+        <v>382</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="C138" s="3">
-        <v>46024</v>
+        <v>383</v>
+      </c>
+      <c r="C138" s="4">
+        <v>2</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>495</v>
+        <v>210</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>285</v>
+        <v>384</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="C139" s="3">
-        <v>46024</v>
+        <v>385</v>
+      </c>
+      <c r="C139" s="4">
+        <v>2</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>495</v>
+        <v>210</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>287</v>
+        <v>386</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C140" s="3">
-        <v>46024</v>
+        <v>387</v>
+      </c>
+      <c r="C140" s="4">
+        <v>2</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>495</v>
+        <v>210</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>289</v>
+        <v>388</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C141" s="3">
-        <v>46024</v>
+        <v>389</v>
+      </c>
+      <c r="C141" s="4">
+        <v>2</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>495</v>
+        <v>210</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>291</v>
+        <v>390</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C142" s="3">
-        <v>46024</v>
+        <v>391</v>
+      </c>
+      <c r="C142" s="4">
+        <v>2</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>495</v>
+        <v>210</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>293</v>
+        <v>392</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="C143" s="3">
-        <v>46024</v>
+        <v>393</v>
+      </c>
+      <c r="C143" s="4">
+        <v>2</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>495</v>
+        <v>210</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>295</v>
+        <v>394</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C144" s="3">
-        <v>46024</v>
+        <v>395</v>
+      </c>
+      <c r="C144" s="4">
+        <v>2</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>495</v>
+        <v>210</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>297</v>
+        <v>396</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="C145" s="3">
-        <v>46024</v>
+        <v>397</v>
+      </c>
+      <c r="C145" s="4">
+        <v>2</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>495</v>
+        <v>210</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>299</v>
+        <v>398</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="C146" s="3">
-        <v>46024</v>
+        <v>399</v>
+      </c>
+      <c r="C146" s="4">
+        <v>2</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>495</v>
+        <v>210</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>301</v>
+        <v>400</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="C147" s="3">
-        <v>46024</v>
+        <v>401</v>
+      </c>
+      <c r="C147" s="4">
+        <v>2</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>495</v>
+        <v>210</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>303</v>
+        <v>402</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="C148" s="3">
-        <v>46024</v>
+        <v>403</v>
+      </c>
+      <c r="C148" s="4">
+        <v>2</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>495</v>
+        <v>210</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>305</v>
+        <v>404</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C149" s="3">
-        <v>46024</v>
+        <v>405</v>
+      </c>
+      <c r="C149" s="4">
+        <v>2</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>496</v>
+        <v>211</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>107</v>
+        <v>292</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>307</v>
+        <v>406</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="C150" s="3">
-        <v>46024</v>
+        <v>407</v>
+      </c>
+      <c r="C150" s="4">
+        <v>2</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>497</v>
+        <v>212</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>309</v>
+        <v>408</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C151" s="3">
-        <v>46024</v>
+        <v>409</v>
+      </c>
+      <c r="C151" s="4">
+        <v>2</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>497</v>
+        <v>212</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>110</v>
+        <v>295</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>311</v>
+        <v>410</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="C152" s="3">
-        <v>46024</v>
+        <v>411</v>
+      </c>
+      <c r="C152" s="4">
+        <v>2</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>498</v>
+        <v>229</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>104</v>
+        <v>289</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>313</v>
+        <v>412</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="C153" s="3">
-        <v>46024</v>
+        <v>413</v>
+      </c>
+      <c r="C153" s="4">
+        <v>2</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>499</v>
+        <v>213</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>110</v>
+        <v>295</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>315</v>
+        <v>414</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C154" s="3">
-        <v>46024</v>
+        <v>415</v>
+      </c>
+      <c r="C154" s="4">
+        <v>2</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>496</v>
+        <v>211</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>110</v>
+        <v>295</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>317</v>
+        <v>416</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="C155" s="3">
-        <v>46024</v>
+        <v>417</v>
+      </c>
+      <c r="C155" s="4">
+        <v>2</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>496</v>
+        <v>211</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>107</v>
+        <v>292</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>319</v>
+        <v>418</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="C156" s="3">
-        <v>46024</v>
+        <v>419</v>
+      </c>
+      <c r="C156" s="4">
+        <v>2</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>497</v>
+        <v>212</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>321</v>
+        <v>420</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
-        <v>322</v>
+        <v>137</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C157" s="3">
-        <v>46024</v>
+        <v>138</v>
+      </c>
+      <c r="C157" s="4">
+        <v>2</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>497</v>
+        <v>212</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>110</v>
+        <v>295</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>324</v>
+        <v>139</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="C158" s="3">
-        <v>46024</v>
+        <v>140</v>
+      </c>
+      <c r="C158" s="4">
+        <v>2</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>497</v>
+        <v>212</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>110</v>
+        <v>295</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
-        <v>326</v>
+        <v>141</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="C159" s="3">
-        <v>46024</v>
+        <v>142</v>
+      </c>
+      <c r="C159" s="4">
+        <v>2</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>500</v>
+        <v>214</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
-        <v>328</v>
+        <v>143</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="C160" s="3">
-        <v>46024</v>
+        <v>144</v>
+      </c>
+      <c r="C160" s="4">
+        <v>2</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>500</v>
+        <v>214</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>330</v>
+        <v>421</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C161" s="3">
-        <v>46024</v>
+        <v>422</v>
+      </c>
+      <c r="C161" s="4">
+        <v>2</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>500</v>
+        <v>214</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>332</v>
+        <v>423</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="C162" s="3">
-        <v>46024</v>
+        <v>424</v>
+      </c>
+      <c r="C162" s="4">
+        <v>2</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>500</v>
+        <v>214</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>334</v>
+        <v>425</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="C163" s="3">
-        <v>46024</v>
+        <v>426</v>
+      </c>
+      <c r="C163" s="4">
+        <v>2</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>500</v>
+        <v>214</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>336</v>
+        <v>427</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="C164" s="3">
-        <v>46024</v>
+        <v>428</v>
+      </c>
+      <c r="C164" s="4">
+        <v>2</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>500</v>
+        <v>214</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
-        <v>337</v>
+        <v>429</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="C165" s="3">
-        <v>46024</v>
+        <v>430</v>
+      </c>
+      <c r="C165" s="4">
+        <v>2</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>500</v>
+        <v>214</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>339</v>
+        <v>431</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>340</v>
+        <v>432</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="C166" s="3">
-        <v>46024</v>
+        <v>433</v>
+      </c>
+      <c r="C166" s="4">
+        <v>2</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>500</v>
+        <v>214</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>342</v>
+        <v>434</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
-        <v>343</v>
+        <v>435</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="C167" s="3">
-        <v>46024</v>
+        <v>436</v>
+      </c>
+      <c r="C167" s="4">
+        <v>2</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>500</v>
+        <v>214</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
-        <v>344</v>
+        <v>437</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="C168" s="3">
-        <v>46024</v>
+        <v>438</v>
+      </c>
+      <c r="C168" s="4">
+        <v>2</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>500</v>
+        <v>214</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>346</v>
+        <v>439</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
-        <v>347</v>
+        <v>440</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="C169" s="3">
-        <v>46024</v>
+        <v>441</v>
+      </c>
+      <c r="C169" s="4">
+        <v>2</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>500</v>
+        <v>214</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>346</v>
+        <v>439</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>349</v>
+        <v>145</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="C170" s="3">
-        <v>46024</v>
+        <v>190</v>
+      </c>
+      <c r="C170" s="4">
+        <v>2</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>500</v>
+        <v>214</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>350</v>
+        <v>146</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="C171" s="3">
-        <v>46024</v>
+        <v>147</v>
+      </c>
+      <c r="C171" s="4">
+        <v>2</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>501</v>
+        <v>215</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>352</v>
+        <v>442</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C172" s="3">
-        <v>46024</v>
+        <v>443</v>
+      </c>
+      <c r="C172" s="4">
+        <v>2</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>501</v>
+        <v>215</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
-        <v>354</v>
+        <v>444</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="C173" s="3">
-        <v>46024</v>
+        <v>445</v>
+      </c>
+      <c r="C173" s="4">
+        <v>2</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>501</v>
+        <v>215</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>356</v>
+        <v>446</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="C174" s="3">
-        <v>46024</v>
+        <v>447</v>
+      </c>
+      <c r="C174" s="4">
+        <v>2</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>501</v>
+        <v>215</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>358</v>
+        <v>448</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C175" s="3">
-        <v>46024</v>
+        <v>449</v>
+      </c>
+      <c r="C175" s="4">
+        <v>2</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>501</v>
+        <v>215</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="C176" s="3">
-        <v>46024</v>
+        <v>451</v>
+      </c>
+      <c r="C176" s="4">
+        <v>2</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>501</v>
+        <v>215</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
-        <v>362</v>
+        <v>452</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="C177" s="3">
-        <v>46024</v>
+        <v>453</v>
+      </c>
+      <c r="C177" s="4">
+        <v>2</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>501</v>
+        <v>215</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>364</v>
+        <v>454</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="C178" s="3">
-        <v>46024</v>
+        <v>455</v>
+      </c>
+      <c r="C178" s="4">
+        <v>2</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>501</v>
+        <v>215</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
-        <v>366</v>
+        <v>456</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="C179" s="3">
-        <v>46024</v>
+        <v>457</v>
+      </c>
+      <c r="C179" s="4">
+        <v>2</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>501</v>
+        <v>215</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>368</v>
+        <v>458</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="C180" s="3">
-        <v>46024</v>
+        <v>459</v>
+      </c>
+      <c r="C180" s="4">
+        <v>2</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>501</v>
+        <v>215</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>370</v>
+        <v>460</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="C181" s="3">
-        <v>46024</v>
+        <v>461</v>
+      </c>
+      <c r="C181" s="4">
+        <v>2</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>501</v>
+        <v>215</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>372</v>
+        <v>462</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="C182" s="3">
-        <v>46024</v>
+        <v>463</v>
+      </c>
+      <c r="C182" s="4">
+        <v>2</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>501</v>
+        <v>215</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="183" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
-        <v>374</v>
+        <v>148</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="C183" s="3">
-        <v>46056</v>
+        <v>149</v>
+      </c>
+      <c r="C183" s="4">
+        <v>2</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
-        <v>376</v>
+        <v>465</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="C184" s="1">
+        <v>466</v>
+      </c>
+      <c r="C184" s="4">
         <v>1</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>378</v>
+        <v>150</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
-        <v>379</v>
+        <v>467</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="C185" s="1">
+        <v>468</v>
+      </c>
+      <c r="C185" s="4">
         <v>1</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>378</v>
+        <v>150</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>381</v>
+        <v>469</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="C186" s="3">
-        <v>46024</v>
+        <v>470</v>
+      </c>
+      <c r="C186" s="4">
+        <v>2</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
-        <v>383</v>
+        <v>471</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="C187" s="3">
-        <v>46024</v>
+        <v>472</v>
+      </c>
+      <c r="C187" s="4">
+        <v>2</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
-        <v>384</v>
+        <v>473</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="C188" s="1">
+        <v>474</v>
+      </c>
+      <c r="C188" s="4">
         <v>2</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>386</v>
+        <v>475</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
-        <v>387</v>
+        <v>476</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="C189" s="3">
-        <v>46024</v>
+        <v>477</v>
+      </c>
+      <c r="C189" s="4">
+        <v>2</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
-        <v>388</v>
+        <v>478</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="C190" s="1">
+        <v>479</v>
+      </c>
+      <c r="C190" s="4">
         <v>2</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>386</v>
+        <v>475</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
-        <v>390</v>
+        <v>480</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="C191" s="1">
+        <v>481</v>
+      </c>
+      <c r="C191" s="4">
         <v>2</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>386</v>
+        <v>475</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
-        <v>392</v>
+        <v>482</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="C192" s="1">
+        <v>483</v>
+      </c>
+      <c r="C192" s="4">
         <v>2</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>386</v>
+        <v>475</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
-        <v>394</v>
+        <v>484</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="C193" s="3">
-        <v>46024</v>
+        <v>485</v>
+      </c>
+      <c r="C193" s="4">
+        <v>2</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
-        <v>396</v>
+        <v>151</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="C194" s="3">
-        <v>46024</v>
+        <v>152</v>
+      </c>
+      <c r="C194" s="4">
+        <v>2</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
-        <v>398</v>
+        <v>153</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="C195" s="3">
-        <v>46024</v>
+        <v>154</v>
+      </c>
+      <c r="C195" s="4">
+        <v>2</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
-        <v>400</v>
+        <v>155</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="C196" s="3">
-        <v>46024</v>
+        <v>156</v>
+      </c>
+      <c r="C196" s="4">
+        <v>2</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
-        <v>402</v>
+        <v>157</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="C197" s="3">
-        <v>46024</v>
+        <v>158</v>
+      </c>
+      <c r="C197" s="4">
+        <v>2</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
-        <v>404</v>
+        <v>159</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="C198" s="3">
-        <v>46024</v>
+        <v>160</v>
+      </c>
+      <c r="C198" s="4">
+        <v>2</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>503</v>
+        <v>230</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
-        <v>406</v>
+        <v>161</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C199" s="3">
-        <v>46024</v>
+        <v>162</v>
+      </c>
+      <c r="C199" s="4">
+        <v>2</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>503</v>
+        <v>230</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
-        <v>408</v>
+        <v>487</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="C200" s="3">
-        <v>46024</v>
+        <v>488</v>
+      </c>
+      <c r="C200" s="4">
+        <v>2</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>503</v>
+        <v>230</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="201" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
-        <v>410</v>
+        <v>489</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="C201" s="3">
-        <v>46024</v>
+        <v>490</v>
+      </c>
+      <c r="C201" s="4">
+        <v>2</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>503</v>
+        <v>230</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>412</v>
+        <v>163</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
-        <v>413</v>
+        <v>491</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C202" s="3">
-        <v>46024</v>
+        <v>492</v>
+      </c>
+      <c r="C202" s="4">
+        <v>2</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>503</v>
+        <v>230</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>412</v>
+        <v>163</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="203" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
-        <v>415</v>
+        <v>493</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C203" s="3">
-        <v>46024</v>
+        <v>494</v>
+      </c>
+      <c r="C203" s="4">
+        <v>2</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>503</v>
+        <v>230</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>412</v>
+        <v>163</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
-        <v>417</v>
+        <v>495</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="C204" s="3">
-        <v>46024</v>
+        <v>496</v>
+      </c>
+      <c r="C204" s="4">
+        <v>2</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>503</v>
+        <v>230</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>412</v>
+        <v>163</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="205" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
-        <v>419</v>
+        <v>164</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C205" s="3">
-        <v>46024</v>
+        <v>165</v>
+      </c>
+      <c r="C205" s="4">
+        <v>2</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>503</v>
+        <v>230</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>421</v>
+        <v>166</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
-        <v>422</v>
+        <v>167</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="C206" s="3">
-        <v>46024</v>
+        <v>168</v>
+      </c>
+      <c r="C206" s="4">
+        <v>2</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>504</v>
+        <v>216</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>246</v>
+        <v>372</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="207" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="C207" s="3">
-        <v>46024</v>
+        <v>498</v>
+      </c>
+      <c r="C207" s="4">
+        <v>2</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>496</v>
+        <v>211</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>426</v>
+        <v>499</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
-        <v>427</v>
+        <v>169</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C208" s="3">
-        <v>46024</v>
+        <v>170</v>
+      </c>
+      <c r="C208" s="4">
+        <v>2</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>505</v>
+        <v>231</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>426</v>
+        <v>499</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="209" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
-        <v>429</v>
+        <v>500</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C209" s="1">
+        <v>501</v>
+      </c>
+      <c r="C209" s="4">
         <v>1</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>504</v>
+        <v>216</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="210" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
-        <v>431</v>
+        <v>502</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="C210" s="3">
-        <v>46024</v>
+        <v>503</v>
+      </c>
+      <c r="C210" s="4">
+        <v>2</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>506</v>
+        <v>232</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>433</v>
+        <v>171</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
-        <v>434</v>
+        <v>172</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="C211" s="3">
-        <v>46024</v>
+        <v>173</v>
+      </c>
+      <c r="C211" s="4">
+        <v>2</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>506</v>
+        <v>232</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>246</v>
+        <v>372</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
-        <v>436</v>
+        <v>174</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="C212" s="3">
-        <v>46024</v>
+        <v>175</v>
+      </c>
+      <c r="C212" s="4">
+        <v>2</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>507</v>
+        <v>233</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>246</v>
+        <v>372</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
-        <v>438</v>
+        <v>176</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C213" s="1">
+        <v>177</v>
+      </c>
+      <c r="C213" s="4">
         <v>1</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>504</v>
+        <v>216</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
-        <v>440</v>
+        <v>178</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="C214" s="3">
-        <v>46024</v>
+        <v>179</v>
+      </c>
+      <c r="C214" s="4">
+        <v>2</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>505</v>
+        <v>231</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>442</v>
+        <v>504</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="215" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
-        <v>443</v>
+        <v>505</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="C215" s="3">
-        <v>46024</v>
+        <v>506</v>
+      </c>
+      <c r="C215" s="4">
+        <v>2</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>508</v>
+        <v>217</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="216" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
-        <v>445</v>
+        <v>507</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="C216" s="3">
-        <v>46024</v>
+        <v>508</v>
+      </c>
+      <c r="C216" s="4">
+        <v>2</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>508</v>
+        <v>217</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="217" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
-        <v>447</v>
+        <v>180</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="C217" s="3">
-        <v>46024</v>
+        <v>181</v>
+      </c>
+      <c r="C217" s="4">
+        <v>2</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>508</v>
+        <v>217</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="218" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
-        <v>449</v>
+        <v>182</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="C218" s="3">
-        <v>46024</v>
+        <v>183</v>
+      </c>
+      <c r="C218" s="4">
+        <v>2</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>508</v>
+        <v>217</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>104</v>
+        <v>289</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Faculties/Natural Science/Postgrad Modules Natural Science.xlsx
+++ b/Faculties/Natural Science/Postgrad Modules Natural Science.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mwamb\OneDrive\Desktop\Team_6_repo\Team19\Faculties\Natural Science\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d24d4a286855a075/Desktop/Team_6_repo/Team19/Faculties/Natural Science/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F567E086-A037-418A-826A-1B2777668633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{F567E086-A037-418A-826A-1B2777668633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3517E59-9E5D-4E01-8B30-FEC09F316CD6}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1091" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="822">
   <si>
     <t>Programmes</t>
   </si>
@@ -1552,6 +1552,969 @@
   </si>
   <si>
     <t>Contemporary Business Analysis 842</t>
+  </si>
+  <si>
+    <t>Learning Outcome</t>
+  </si>
+  <si>
+    <t>Credits</t>
+  </si>
+  <si>
+    <t>Main Content</t>
+  </si>
+  <si>
+    <t>Conduct extensive literature research; perform independent field or laboratory research.</t>
+  </si>
+  <si>
+    <t>Evaluate and understand advanced geological Earth materials.</t>
+  </si>
+  <si>
+    <t>Apply geochemical principles to independent research.</t>
+  </si>
+  <si>
+    <r>
+      <t>Consult Department</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for outcomes.</t>
+    </r>
+  </si>
+  <si>
+    <t>Conduct research; prepare reports and presentations for communicating findings.</t>
+  </si>
+  <si>
+    <t>Apply EM theory to physics; calculate energy in electromagnetic radiation.</t>
+  </si>
+  <si>
+    <t>Calculate stellar properties and light output; explain galaxy evolution.</t>
+  </si>
+  <si>
+    <t>Write programs for astrophysical problems; solve differential equations.</t>
+  </si>
+  <si>
+    <t>Scientific Programming for Astrophysics and Space Science.</t>
+  </si>
+  <si>
+    <t>Calculate atomic properties and statistical distributions for stars and galaxies.</t>
+  </si>
+  <si>
+    <t>Explain geospace characteristics; calculate plasma parameters.</t>
+  </si>
+  <si>
+    <t>Describe issues around galaxy formation and evolution.</t>
+  </si>
+  <si>
+    <t>Apply Maxwell’s Equations; calculate energy/momentum in EM fields.</t>
+  </si>
+  <si>
+    <t>Execute research under supervision; communicate findings in oral/written formats.</t>
+  </si>
+  <si>
+    <t>Understand species concepts, nomenclature, and find taxonomic info.</t>
+  </si>
+  <si>
+    <t>Analyse spatial information; model info for resource management.</t>
+  </si>
+  <si>
+    <t>Design and execute marine biological field studies and write professional reports.</t>
+  </si>
+  <si>
+    <t>Converse on herpetological diversity; contribute data to national databases.</t>
+  </si>
+  <si>
+    <t>Understand research process; evaluate and critique scientific publications.</t>
+  </si>
+  <si>
+    <t>Understand mechanisms determining diversity; collect ecological data.</t>
+  </si>
+  <si>
+    <t>Design experiments; use biostatistical analysis software.</t>
+  </si>
+  <si>
+    <t>Practical and technical experience; laboratory safety knowhow.</t>
+  </si>
+  <si>
+    <t>Perform literature surveys; construct scientific introductions.</t>
+  </si>
+  <si>
+    <t>Understand advanced plant biotechnology topics.</t>
+  </si>
+  <si>
+    <t>Calculate DNA profile matching probability for court evidence.</t>
+  </si>
+  <si>
+    <t>Specialist study of a topic within Biotechnology.</t>
+  </si>
+  <si>
+    <t>Understand biofuel types and value chain improvements.</t>
+  </si>
+  <si>
+    <t>Understand cancer manifestations and oncogene regulation.</t>
+  </si>
+  <si>
+    <t>Understand various sequencing technologies and novel applications.</t>
+  </si>
+  <si>
+    <t>Apply MS, NMR, and IR spectroscopy methods.</t>
+  </si>
+  <si>
+    <t>Use word/spreadsheet software; work in cooperative groups.</t>
+  </si>
+  <si>
+    <t>Apply chemical trends of main group elements to rings/cages.</t>
+  </si>
+  <si>
+    <t>Calculate rate constants and thermodynamic parameters.</t>
+  </si>
+  <si>
+    <t>Describe polymer types and mechanisms of polymerization.</t>
+  </si>
+  <si>
+    <t>Perform advanced study in specialist selection of topics.</t>
+  </si>
+  <si>
+    <t>Define business needs; utilise theoretical knowledge for data solutions.</t>
+  </si>
+  <si>
+    <t>Apply large number laws; generate random observations.</t>
+  </si>
+  <si>
+    <t>Summarize knowledge and analyze finance problems.</t>
+  </si>
+  <si>
+    <t>Apply laws of large numbers and central limit theorem.</t>
+  </si>
+  <si>
+    <t>Applied financial engineering and stochastic calculus.</t>
+  </si>
+  <si>
+    <t>Understand pricing of derivatives instruments.</t>
+  </si>
+  <si>
+    <t>Summarise knowledge and analyse risk management problems.</t>
+  </si>
+  <si>
+    <t>Interpret/implement principles and tools for quality software development.</t>
+  </si>
+  <si>
+    <t>Analyse and document business requirements and processes.</t>
+  </si>
+  <si>
+    <t>Apply project management concepts (scope, budget, risk).</t>
+  </si>
+  <si>
+    <t>Understand the role of technology in development.</t>
+  </si>
+  <si>
+    <t>Handle and engineer big data sets.</t>
+  </si>
+  <si>
+    <t>Apply artificial intelligence concepts and tools.</t>
+  </si>
+  <si>
+    <t>Evaluate and use cloud computing infrastructure.</t>
+  </si>
+  <si>
+    <t>Use AI concepts to solve practical problems.</t>
+  </si>
+  <si>
+    <t>Design immersive technology solutions.</t>
+  </si>
+  <si>
+    <t>Critically review environmental and water legislation.</t>
+  </si>
+  <si>
+    <t>Perform advanced GIS data query and spatial analysis.</t>
+  </si>
+  <si>
+    <t>Describe hydro-geologic systems and water chemistry.</t>
+  </si>
+  <si>
+    <t>Describe surface water hydrology and processes.</t>
+  </si>
+  <si>
+    <t>Perform supervised research project or internship.</t>
+  </si>
+  <si>
+    <t>Use measure theory and carry out mathematical proofs.</t>
+  </si>
+  <si>
+    <t>Matrix theory and linear algebra applications.</t>
+  </si>
+  <si>
+    <t>Explain mathematical physics principles.</t>
+  </si>
+  <si>
+    <t>Use coding theory to prove mathematical statements.</t>
+  </si>
+  <si>
+    <t>Conduct research; analyze and report findings.</t>
+  </si>
+  <si>
+    <t>Advanced algebra involving Rings and Modules.</t>
+  </si>
+  <si>
+    <t>Specialist Module in Epidemiology 701.</t>
+  </si>
+  <si>
+    <t>Execute advanced technique studies in bioscience.</t>
+  </si>
+  <si>
+    <t>Complete independent research project.</t>
+  </si>
+  <si>
+    <t>Knowledge of anatomical histology and molecular techniques.</t>
+  </si>
+  <si>
+    <t>Measure immune signaling via various assays.</t>
+  </si>
+  <si>
+    <t>Explain physiological adaptations to training types.</t>
+  </si>
+  <si>
+    <t>Understand áreas of signals and telecommunications.</t>
+  </si>
+  <si>
+    <t>Solve problems associated with accelerators.</t>
+  </si>
+  <si>
+    <t>Explain stat mech and quantum principles.</t>
+  </si>
+  <si>
+    <t>Apply theory of crystals; study electronic properties.</t>
+  </si>
+  <si>
+    <t>Apply advanced concepts in Materials Science.</t>
+  </si>
+  <si>
+    <t>Understand photon based analytical techniques.</t>
+  </si>
+  <si>
+    <t>Evaluate demographic analysis data.</t>
+  </si>
+  <si>
+    <t>Gender Issues and Reproductive Health.</t>
+  </si>
+  <si>
+    <t>Social Demography.</t>
+  </si>
+  <si>
+    <t>Develop short research proposal.</t>
+  </si>
+  <si>
+    <t>Critically apply data analysis techniques.</t>
+  </si>
+  <si>
+    <t>Design research methodology and produce proposal.</t>
+  </si>
+  <si>
+    <t>Apply knowledge of statistical inference.</t>
+  </si>
+  <si>
+    <t>Prepare and analyse dataset via statistical package.</t>
+  </si>
+  <si>
+    <t>Make scope-limited contribution to stats/demography.</t>
+  </si>
+  <si>
+    <t>Critique application of IWRM in project context.</t>
+  </si>
+  <si>
+    <t>Describe water resources system principles.</t>
+  </si>
+  <si>
+    <t>Explain management tools for natural resources.</t>
+  </si>
+  <si>
+    <t>Review and interpret mathematical material.</t>
+  </si>
+  <si>
+    <t>Communication Skills, Computing and LaTeX.</t>
+  </si>
+  <si>
+    <t>Mathematical Problem Solving.</t>
+  </si>
+  <si>
+    <t>Gain research experience in problem solving.</t>
+  </si>
+  <si>
+    <t>Embark on advanced work in cutting edge physics.</t>
+  </si>
+  <si>
+    <t>Evaluate residuals; use ARIMA models.</t>
+  </si>
+  <si>
+    <t>Describe structural macromolecules/biological forces.</t>
+  </si>
+  <si>
+    <t>48*</t>
+  </si>
+  <si>
+    <t>Experimental Techniques in Nanochemistry.</t>
+  </si>
+  <si>
+    <t>16*</t>
+  </si>
+  <si>
+    <t>Experimental Techniques in Nanophysics.</t>
+  </si>
+  <si>
+    <t>Pharmacy Admin and Policy Mini-Thesis.</t>
+  </si>
+  <si>
+    <t>Interpret regulation of Generic medicines.</t>
+  </si>
+  <si>
+    <t>Regulatory Science and Medical Devices.</t>
+  </si>
+  <si>
+    <r>
+      <t>Consult School of Pharmacy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for outcomes.</t>
+    </r>
+  </si>
+  <si>
+    <t>Pharmacology Mini-Thesis.</t>
+  </si>
+  <si>
+    <t>60*</t>
+  </si>
+  <si>
+    <t>10*</t>
+  </si>
+  <si>
+    <t>Use second quantisation; solve relativistic problems.</t>
+  </si>
+  <si>
+    <t>Use Green functions; calculate phonon properties.</t>
+  </si>
+  <si>
+    <t>Explain effect of curriculum on learning.</t>
+  </si>
+  <si>
+    <t>Use Tensor analysis; solve scattering problems.</t>
+  </si>
+  <si>
+    <t>Critical analysis of reproductive health data.</t>
+  </si>
+  <si>
+    <t>Analysis of gender equity and contraception.</t>
+  </si>
+  <si>
+    <t>Produce scientific report of findings.</t>
+  </si>
+  <si>
+    <t>Contribution to field of Statistics following research.</t>
+  </si>
+  <si>
+    <t>Contribution to field of Stats/Demography knowledge.</t>
+  </si>
+  <si>
+    <t>Critically analyse multivariate data sets.</t>
+  </si>
+  <si>
+    <t>Contribution with limited scope to Statistics/Data Science.</t>
+  </si>
+  <si>
+    <t>Mine text; analyse web, geospatial, and customer data.</t>
+  </si>
+  <si>
+    <t>Critically utilise matrix operations in statistical context.</t>
+  </si>
+  <si>
+    <t>Pharmacology Postgraduate Modules; Content restricted - consult School of Pharmacy.</t>
+  </si>
+  <si>
+    <t>Quantum Mechanics 820.</t>
+  </si>
+  <si>
+    <t>Second quantisation; Dirac equation; Relativistic Quantum Mechanics; Scattering theory.</t>
+  </si>
+  <si>
+    <t>Nuclear models; Nuclear reactions; Interface between low energy nuclear physics and particle physics.</t>
+  </si>
+  <si>
+    <t>Physics Education: impact of curriculum on learning.</t>
+  </si>
+  <si>
+    <t>Tensor analysis; Complex analysis; Sturm Liouville theory; Integral equations; Green functions.</t>
+  </si>
+  <si>
+    <t>Advanced Demographic Analysis.</t>
+  </si>
+  <si>
+    <t>Official Statistics 809.</t>
+  </si>
+  <si>
+    <t>Survey Methods for Population Studies.</t>
+  </si>
+  <si>
+    <t>Population Projections 812.</t>
+  </si>
+  <si>
+    <t>African Historical Demography 813.</t>
+  </si>
+  <si>
+    <t>Social Demography 814.</t>
+  </si>
+  <si>
+    <t>Gender Issues and Reproductive Health 815.</t>
+  </si>
+  <si>
+    <t>Mathematical Demography and Population Modelling 848.</t>
+  </si>
+  <si>
+    <t>Advanced Data Mining II.</t>
+  </si>
+  <si>
+    <t>Statistics Master’s Thesis research and production.</t>
+  </si>
+  <si>
+    <t>Statistics Master’s Mini-Thesis research and production.</t>
+  </si>
+  <si>
+    <t>Advanced Research Methodology.</t>
+  </si>
+  <si>
+    <t>Advanced Multivariate Analysis.</t>
+  </si>
+  <si>
+    <t>Advanced Experimental Design.</t>
+  </si>
+  <si>
+    <t>Biostatistics in clinical/health research.</t>
+  </si>
+  <si>
+    <t>Statistical Genetics 837.</t>
+  </si>
+  <si>
+    <t>conceptual foundations of industry research; project planning; objectives formulation; design/measurement; report writing.</t>
+  </si>
+  <si>
+    <t>Business Intelligence techniques; ethical data handling; prepare big data for mining; analytical tools.</t>
+  </si>
+  <si>
+    <t>Contemporary Business Analysis 842.</t>
+  </si>
+  <si>
+    <t>Multicriteria Decision Making 843.</t>
+  </si>
+  <si>
+    <t>Vector and Matrix theory for advanced statistics.</t>
+  </si>
+  <si>
+    <t>Probability/Statistics; Number Theory; Algorithms; Complex Analysis; Algebra; Numerical Analysis; Algebraic Graph Theory; Robotics.</t>
+  </si>
+  <si>
+    <t>Computational Finance 817.</t>
+  </si>
+  <si>
+    <t>International Finance 818.</t>
+  </si>
+  <si>
+    <t>finance application software; data structures and algorithms; project work.</t>
+  </si>
+  <si>
+    <t>Theoretical Statistics 826.</t>
+  </si>
+  <si>
+    <t>Financial Risk Management 827.</t>
+  </si>
+  <si>
+    <t>Probability and Stochastic Processes 828.</t>
+  </si>
+  <si>
+    <t>EDA; difference equations; ARIMA models/seasonality; estimation/prediction; Spectral density functions; SPSS.</t>
+  </si>
+  <si>
+    <t>Statistical Arbitrage 832.</t>
+  </si>
+  <si>
+    <t>Credit Derivatives 835.</t>
+  </si>
+  <si>
+    <t>Linear Financial Models 836.</t>
+  </si>
+  <si>
+    <t>Research project topics in biomedical sciences, chemistry or physics.</t>
+  </si>
+  <si>
+    <t>History/nature of nanoscience; properties of nanomaterials; tubes/rods/particles; interdisciplinary aspects.</t>
+  </si>
+  <si>
+    <t>Managing innovation; Networks for projects.</t>
+  </si>
+  <si>
+    <t>bionanotechnology synthesis/encapsulation; medical devices/diagnostics; Physiological/Immunological responses; molecular disease origin.</t>
+  </si>
+  <si>
+    <t>live equipment demonstrations; protein expression/purification; molecular biology/genomics; immunoassays.</t>
+  </si>
+  <si>
+    <t>Biological chemistry (bonds, acids, enzymes); Macromolecules (proteins, nucleic acids); cell structure/metabolic processes.</t>
+  </si>
+  <si>
+    <t>Group Theory; advanced characterisation (NMR, XPS, XRD, AFM, Electroanalysis); energy devices; sensors; drug delivery; environmental analysis.</t>
+  </si>
+  <si>
+    <t>ceramics, glasses, polymers; structural properties/crystallography; Tools (FTIR, NMR, UV-Vis, TEM, SEM, AFM, XRD, XPS).</t>
+  </si>
+  <si>
+    <t>Synthesis, nano-structures and nano-devices; characterisation theory; tools (FTIR, Raman, TEM, EDS, EELS, SEM).</t>
+  </si>
+  <si>
+    <t>Quantum physics; nanomaterials (semiconductors, quantum dots); crystallography/reactivities; tools (EBSD, AFM, Auger).</t>
+  </si>
+  <si>
+    <t>pharmaceutical/health ethics; medical research benefit; Humanitarian issues.</t>
+  </si>
+  <si>
+    <t>Administrative/prescribing information; GMP; Non-clinical and clinical study reports.</t>
+  </si>
+  <si>
+    <t>legislation/regulations/science of Biosimilars; quality, safety, efficacy investigation.</t>
+  </si>
+  <si>
+    <t>Complementary and Traditional Medicines and their Regulation.</t>
+  </si>
+  <si>
+    <t>Pharmacovigilance 816.</t>
+  </si>
+  <si>
+    <t>Regulatory Affairs 817.</t>
+  </si>
+  <si>
+    <t>Research Methods 818.</t>
+  </si>
+  <si>
+    <t>Leadership and Negotiations 819.</t>
+  </si>
+  <si>
+    <t>Clinical Trials and Statistics 820.</t>
+  </si>
+  <si>
+    <t>Health Economics 821.</t>
+  </si>
+  <si>
+    <t>Professional Development and Entrepreneurism.</t>
+  </si>
+  <si>
+    <t>Electromagnetism; Relativity; Quantum mechanics; Non-linear waves; Topology; Robotics; Statistical inference; Complex systems.</t>
+  </si>
+  <si>
+    <t>Research topic literature review; research project proposal; geological setting; field and/or laboratory work; obtaining analytical results; interpretation of data; report writing; oral presentation of report.</t>
+  </si>
+  <si>
+    <t>Review of the Geological Time Scale; tectonic evolution of the Kalahari, Congo-Tanzania and West African Cratons; anorogenic and orogenic magmatism; Archaean and Proterozoic Metallogeny (Gold, Tin, Copper); development of sedimentary Basins in Africa; precious/base metal and hydrocarbon potentials; Structural Geology in geotectonic context; stress and origin; deformation mechanisms (compressional, extensional, strike-slip); microtectonics; geological field mapping; analysis of petrographic thin sections.</t>
+  </si>
+  <si>
+    <t>Sample preparation (digestion, extraction); Quality control/assurance; use of GFAAS, XRF and ICP-MS. Low temperature geochemistry: chemical weathering, aqueous geochemistry (speciation, redox), mineral stability diagrams, adsorption. Geochemical prospecting: lithogeochemistry, stream sediment, regolith, biogeochemistry.</t>
+  </si>
+  <si>
+    <t>Mineral economics; geological features of ore deposits; Reconnaissance (desk study, remote sensing); mapping, soil/sediment geochemistry, drilling; Common Geophysical Methods (logging techniques, subsurface characterization); determining depth/structure of bedrock; Exploration data evaluation; Ore resource modelling; reserve estimation.</t>
+  </si>
+  <si>
+    <t>Hydrocarbon accumulation; Sedimentary environments; Basins and sequence stratigraphy; Reservoir Diagenesis; Source Rock Maturity; Hydrocarbon traps; Log/Core Analysis and calibration; Volume estimates; Reserves.</t>
+  </si>
+  <si>
+    <t>Research project in collaboration with an astrophysics supervisor; technical report writing and presentation of findings.</t>
+  </si>
+  <si>
+    <t>Vectors and Tensors; Maxwell's Equations; Electromagnetic Waves; Radiative Processes.</t>
+  </si>
+  <si>
+    <t>Multi-wavelength astronomy focusing on South African research strengths (Stellar Astronomy, Galaxies, Cosmology).</t>
+  </si>
+  <si>
+    <t>Atomic Physics; Statistical Mechanics; Astrophysical Fluid Dynamics.</t>
+  </si>
+  <si>
+    <t>Geospace environment, dynamics and structure; Physics from 50 km above Earth to the magnetopause; plasma physics introduction.</t>
+  </si>
+  <si>
+    <t>General Relativity: Special Relativity; Tensors in SR; Curved Manifolds and Spacetime; Einstein’s Field Equations; Gravitational waves; Black holes.</t>
+  </si>
+  <si>
+    <t>Observational Techniques: Telescopes; Detectors; Photometry; Virtual Observatory; Near Infrared; Polarimetry; Radio telescopes/interferometry; Aperture synthesis; Data Reduction; SALT.</t>
+  </si>
+  <si>
+    <t>Geometry; Observational parameters; Cosmic Wave Background; Early Universe; Large scale structures; Baryon acoustic oscillations; dark energy.</t>
+  </si>
+  <si>
+    <t>Space Technology; Space Weather; Plasma Physics; Fluid Dynamics; Solar Physics; Space waves.</t>
+  </si>
+  <si>
+    <t>Advanced topics including galaxy formation and evolutions based on current local and visiting research.</t>
+  </si>
+  <si>
+    <t>Vectors and Tensors; Maxwell's Equations; EM Waves; Relativity and Electromagnetism; energy and momentum; Single particle motion; Radiative Processes; Antennas.</t>
+  </si>
+  <si>
+    <t>Subject specific research project depending upon the topics offered by staff in any one year.</t>
+  </si>
+  <si>
+    <t>Diversity/evolution of Cape Flora and SA plant/animal families; Red Data Species conservation; modern species concepts; nomenclature; electronic keys; molecular systematic techniques.</t>
+  </si>
+  <si>
+    <t>GIS and remote-sensing; GPS mapping; Geostatistics; species distribution data; Internet mapping; classification of satellite imagery; biodiversity/taxonomic database principles.</t>
+  </si>
+  <si>
+    <t>Pelagic and benthic ecology; physical/chemical oceanography; role of environment in shaping organisms; diversity and functioning of ecosystems; rocky intertidal habitats.</t>
+  </si>
+  <si>
+    <t>Tetrapod evolution; reptile/amphibian systematics/ecology; southern African/global herpetofauna conservation; Field survey, data collection, and research writing.</t>
+  </si>
+  <si>
+    <t>Sampling design; research techniques; lab safety; project proposal; field research planning; data presentation; interpreting scientific data; oral/poster presentations.</t>
+  </si>
+  <si>
+    <t>Species assembly processes (neutral/niche mechanisms); distributional patterns (global/regional/local); R tools; multivariate techniques (nMDS, PCA, RDA, cluster analysis).</t>
+  </si>
+  <si>
+    <t>Training and skills development with appropriate analytical software including SPSS and R; Data management.</t>
+  </si>
+  <si>
+    <t>Molecular basis of viral vector technologies (types, vaccine delivery, gene therapy); Molecular biology practical components.</t>
+  </si>
+  <si>
+    <t>Literature review construction and survey; preparation of scientific introductions; Academic writing.</t>
+  </si>
+  <si>
+    <t>Biotechnology research project; scientific methodology/writing; data analysis; Laboratory/Health/Chemical safety training.</t>
+  </si>
+  <si>
+    <t>Transformation and regeneration; expression systems/gene suppression; Disease and pest resistance; Molecular tools for breeding; Crop modification.</t>
+  </si>
+  <si>
+    <t>DNA/chromosome structure/function; Genes in pedigrees; Physical/genetic mapping; DNA mutations/instability; genome projects; genetic diseases.</t>
+  </si>
+  <si>
+    <t>Cell Cycle (checkpoints, CDKs, inhibitors); Cell Death (Necrosis, Apoptosis, terminal differentiation); Apoptosis and disease.</t>
+  </si>
+  <si>
+    <t>Diversity of food borne microorganisms; adaptations to food environments; food borne pathogens; management of food safety.</t>
+  </si>
+  <si>
+    <t>Scientific basis of DNA typing; forensic procedures (isolation, RFLP, PCR, automated analysis); interpreting results (degradation, multiple contributors); likelihood ratios.</t>
+  </si>
+  <si>
+    <t>Specialist study of a topic within Biotechnology; structure variable to suit topic.</t>
+  </si>
+  <si>
+    <t>Proteomics: sample preparation, quantification, separation; gel/non-gel based comparative analysis; Mass spectrometry identification; applications.</t>
+  </si>
+  <si>
+    <t>Biofuels types (1st/2nd gen); value chain analysis; Biodiesel, biogas, bioethanol; algae; biomass pretreatment; metabolic engineering; drop-in fuels.</t>
+  </si>
+  <si>
+    <t>Nature of cancer; tumour viruses; oncogenes; growth factors/receptors; signalling circuitry; suppressor genes; pRb and cell cycle; p53 and apoptosis.</t>
+  </si>
+  <si>
+    <t>NGS technology (Sanger, 454, Illumina, Ion Torrent); genomics/metagenomics; transcriptomics; viromics; metabolomics.</t>
+  </si>
+  <si>
+    <t>Advanced mass spectroscopy (ion sources, spectral interpretation); Advanced NMR (1H, 13C, COSY, HETCOR, NOE); Advanced atomic spectrometry (GF-AAS, ICP-AES).</t>
+  </si>
+  <si>
+    <t>Terpenes classification; Steroids (conformation, reactivity); Carbohydrates (reactions, nomenclature); Pericyclic reactions; Molecular Orbital Theory; Advanced synthetic methods.</t>
+  </si>
+  <si>
+    <t>Inorganic rings/cages/chains; advanced crystal field theory; molecular orbital theory for coordination complexes; bio-inorganic compounds; organometallic compounds (Alkyls, Alkenes, Carbenes); industrial homogenous catalysis.</t>
+  </si>
+  <si>
+    <t>Homogeneous gas phase reactions; unimolecular reactions; adsorption isotherms; catalysis; quantum mechanical postulates; hydrogen-like atoms; statistical thermodynamics.</t>
+  </si>
+  <si>
+    <t>Homogeneous/heterogenous catalysis in petroleum; electrocatalysis; process design; Temkin adsorption isotherm; characterization of fuel cells; hydrogen economy/storage.</t>
+  </si>
+  <si>
+    <t>Process of research; design, synthesis, characterisation, and quantification relevant to selected mini-project.</t>
+  </si>
+  <si>
+    <t>Biosensors design; Bio-separations; Drug Delivery (micelles, liposomes, NPs); Bio-organic synthesis; Organometallic oxidation/complexes.</t>
+  </si>
+  <si>
+    <t>Engaging with clients to scope business needs; proposed analytics solutions; multi-stakeholder engagement; research reporting; business communication.</t>
+  </si>
+  <si>
+    <t>Monte Carlo Simulation; Finite Difference Methods; Martingales and Measures in Derivatives.</t>
+  </si>
+  <si>
+    <t>Advanced Time Series Analysis techniques and applications.</t>
+  </si>
+  <si>
+    <t>Advanced Probability and Stochastic Processes.</t>
+  </si>
+  <si>
+    <t>Stochastic Calculus for Finance 714.</t>
+  </si>
+  <si>
+    <t>Financial Engineering 716.</t>
+  </si>
+  <si>
+    <t>Risk measurement; analytical methods; value-at-risk methodologies; risk modelling.</t>
+  </si>
+  <si>
+    <t>Formal Methods (Z); Cleanroom SE; Component-Based SE; Web Engineering; Reengineering; CASE tools; recent trends in SE.</t>
+  </si>
+  <si>
+    <t>Requirements Engineering; analysis modeling (UML/OOA); design engineering; user interface design; prototyping; project presentation.</t>
+  </si>
+  <si>
+    <t>Implementation and testing activities within the Software Development Life-cycle; project presentation.</t>
+  </si>
+  <si>
+    <t>Information and Communication Technology for Development.</t>
+  </si>
+  <si>
+    <t>Introduction to the Internet of Things 735.</t>
+  </si>
+  <si>
+    <t>Big Data Engineering 736.</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence 737.</t>
+  </si>
+  <si>
+    <t>Cryptography/Cryptology; algorithms/protocols; Digital Forensics; Legislation and Governance; Malware; Social Engineering; Ethics.</t>
+  </si>
+  <si>
+    <t>4IR Special Topics determined by staff and industrial partners.</t>
+  </si>
+  <si>
+    <t>Cloud deployment/service models; Cloud architectures and protocols; emerging trends; service provisioning.</t>
+  </si>
+  <si>
+    <t>Predictive Categorization (LDA, k-NN); Machine Learning (Regression, Trees, Neural Networks); Text Mining; Generative AI (LLMs); AI Ethics.</t>
+  </si>
+  <si>
+    <t>2D/3D asset development; Good practice for immersive systems; optimisation; basic interactive applications; multimedia integration.</t>
+  </si>
+  <si>
+    <t>C# implementation; application development suite; mobile applications; AR frameworks.</t>
+  </si>
+  <si>
+    <t>Environmental/water law; EIA process (Risk Assessment, Strategic Assessment); specialist studies (biodiversity, hydrogeology); management plans.</t>
+  </si>
+  <si>
+    <t>ArcGIS, ILWIS; spatial analytics; geocoding; multi-criteria analysis; Terrain analysis; geodatabase management; coordinate systems; metadata.</t>
+  </si>
+  <si>
+    <t>Groundwater geophysics; hydraulics; modeling with case studies; geochemical processes; transport/remediation; recharge estimation; governance.</t>
+  </si>
+  <si>
+    <t>precipitation variation; infiltration; evapotranspiration; runoff formation; river flow measurement; flood analysis; remote sensing; yield estimation.</t>
+  </si>
+  <si>
+    <t>Supervised research project or internship.</t>
+  </si>
+  <si>
+    <t>Fluvial geomorphology; river/wetland classification; biogeomorphology; ecological integrity assessment; ecosystem services; degradation and restoration.</t>
+  </si>
+  <si>
+    <t>Ordinary Differential Equations 707.</t>
+  </si>
+  <si>
+    <t>Number Theory 709.</t>
+  </si>
+  <si>
+    <t>Graph Theory 710.</t>
+  </si>
+  <si>
+    <t>Partial Differential Equations 717.</t>
+  </si>
+  <si>
+    <t>Measure and Integration 727.</t>
+  </si>
+  <si>
+    <t>Matrix factorizations (LU, QR); Linear equations (Conditioning, Accuracy); Least squares; Eigenvalue problems; Iterative methods (Jacobi, SOR); SVD.</t>
+  </si>
+  <si>
+    <t>Vector/tensor calculus; special functions; Differential geometry; Hamiltonian mechanics; Relativistic quantum; General Relativity; black hole spacetimes.</t>
+  </si>
+  <si>
+    <t>Category Theory and Order Theory 732.</t>
+  </si>
+  <si>
+    <t>Topology 737.</t>
+  </si>
+  <si>
+    <t>Functions of a Complex Variable 738.</t>
+  </si>
+  <si>
+    <t>Group Theory 739.</t>
+  </si>
+  <si>
+    <t>Error-detection/correction; encoding/decoding; dual codes; finite fields; Reed-Solomon/Reed-Muller codes; burst errors; interleaving.</t>
+  </si>
+  <si>
+    <t>Independent research project topic chosen in consultation with the lecturer.</t>
+  </si>
+  <si>
+    <t>Advanced Rings and Modules 757.</t>
+  </si>
+  <si>
+    <t>Functional Analysis 767.</t>
+  </si>
+  <si>
+    <t>Numerical Analysis 777.</t>
+  </si>
+  <si>
+    <t>Lab calculations/etiquette; Microscopy; ELISA; Bioinformatics; PCR; Western/Dot blots; Chromatography; Cytotoxicity assay.</t>
+  </si>
+  <si>
+    <t>project selection/planning; Budget; Protocol writing; execution; data interpretation; writing of scientific report; public lecture.</t>
+  </si>
+  <si>
+    <t>molecular techniques; writing/publishing reports; specialised anatomical dissection sessions.</t>
+  </si>
+  <si>
+    <t>Microbiology of Female Morbidity 707.</t>
+  </si>
+  <si>
+    <t>Apoptosis and Cell Signalling 709.</t>
+  </si>
+  <si>
+    <t>foetal origins hypothesis; role of placenta; maternal nutrition and lifestyle consequences on adult health.</t>
+  </si>
+  <si>
+    <t>Advanced Studies in Reproduction and Health 713.</t>
+  </si>
+  <si>
+    <t>antibody production; ELISA; Western Blotting; lymphocyte stimulation; reporter assays; immune signaling measurement.</t>
+  </si>
+  <si>
+    <t>Applied Exercise Science 715.</t>
+  </si>
+  <si>
+    <t>Nutrition in Health and Disease 716.</t>
+  </si>
+  <si>
+    <t>Research Module in signals and telecommunications.</t>
+  </si>
+  <si>
+    <t>Quantum Physics (Hilbert space, operators); Mathematical Methods; Electromagnetism; Computational Python/Matlab; Monte Carlo; Mathematica analysis.</t>
+  </si>
+  <si>
+    <t>Accelerator Overview; AC optics; diagnostics; Linear Accelerators; beam optics; RF/Vacuum/Injection/Extraction systems; applications.</t>
+  </si>
+  <si>
+    <t>Thermodynamic probability; perfect gas state; Legendre Transforms; Bose-Einstein/Fermi-Dirac distributions; Scattering; Approximations; X-ray Spectra.</t>
+  </si>
+  <si>
+    <t>Shell/Collective models; NAC experimental methods; isotopes; reactor physics; environmental radioactivity (Radon).</t>
+  </si>
+  <si>
+    <t>Crystalline/amorphous semiconductors; band theory; transport/mobility; Recombination; P-N Junctions; photovoltaic solar cell.</t>
+  </si>
+  <si>
+    <t>Diffusion; Phase diagrams; Mechanical properties; Metals; Polymers/composites; Magnetic materials; superconductors; photovoltaics.</t>
+  </si>
+  <si>
+    <t>Electron Microscopy (SEM, EDS, TEM); preparation techniques; STM; AFM; Hall effect measurements; Profilometry.</t>
+  </si>
+  <si>
+    <t>Official Statistics 703.</t>
+  </si>
+  <si>
+    <t>Demographic Analysis 707.</t>
+  </si>
+  <si>
+    <t>population dynamics functions (exponential, stable, stationary); modeling and development planning.</t>
+  </si>
+  <si>
+    <t>Short research proposal development in population studies.</t>
+  </si>
+  <si>
+    <t>Applied Statistics 501.</t>
+  </si>
+  <si>
+    <t>Multivariate Analysis 701.</t>
+  </si>
+  <si>
+    <t>Research Methodology 702.</t>
+  </si>
+  <si>
+    <t>Theoretical Statistics 705.</t>
+  </si>
+  <si>
+    <t>Experimental Design 710.</t>
+  </si>
+  <si>
+    <t>Biostatistics 733.</t>
+  </si>
+  <si>
+    <t>Statistical Genetics 736.</t>
+  </si>
+  <si>
+    <t>Statistical Modelling 737.</t>
+  </si>
+  <si>
+    <t>Applied Analytics 738.</t>
+  </si>
+  <si>
+    <t>Introductory Multivariate Analysis 739.</t>
+  </si>
+  <si>
+    <t>Data Mining I 760.</t>
+  </si>
+  <si>
+    <t>Honors Project contribution to Stats/Demography.</t>
+  </si>
+  <si>
+    <t>Projections by sex/age; urban/rural; labour force; households; school enrolments; education level; computerized applications.</t>
+  </si>
+  <si>
+    <t>IWRM in Practice 731.</t>
+  </si>
+  <si>
+    <t>Water resources system; planning/implementation; protection/policy; assessment/monitoring; sectors demand; allocation/licensing; institutions/governance.</t>
+  </si>
+  <si>
+    <t>GIS/remote sensing data management; Terrain analysis; spectral indices (vegetation, water, fire); analytical modelling; suitability mapping.</t>
+  </si>
+  <si>
+    <t>Environmental Management and Water Regulations 734.</t>
+  </si>
+  <si>
+    <t>surface/groundwater quality variation processes; classification; sampling design; field equipment; QA/QC reporting.</t>
+  </si>
+  <si>
+    <t>Ecosystem classification; applied fluvial geomorphology; river/wetland dynamics; integrity bioindicators; ecosystem services measurement/management.</t>
+  </si>
+  <si>
+    <t>Environmental Education and Water Security 737.</t>
+  </si>
+  <si>
+    <t>Water Demand Management for Sustainable Development 738.</t>
+  </si>
+  <si>
+    <t>Mini-thesis research project.</t>
+  </si>
+  <si>
+    <t>Physics of moving objects; electrodynamics; gravity; molecular movement; elementary particles.</t>
+  </si>
+  <si>
+    <t>imperative programming (sequential, iterative); Modularity; files/strings; overview of scipy library.</t>
+  </si>
+  <si>
+    <t>computational tools/methods; analysis, number theory and linear algebra problems.</t>
   </si>
 </sst>
 </file>
@@ -1595,7 +2558,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1610,6 +2573,13 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1625,6 +2595,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1890,14 +2864,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F218"/>
+  <dimension ref="A1:I218"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="8.88671875" style="5"/>
     <col min="4" max="4" width="23.21875" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>218</v>
       </c>
@@ -1916,8 +2891,17 @@
       <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G1" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="360" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1936,8 +2920,17 @@
       <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G2" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="I2" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>235</v>
       </c>
@@ -1956,8 +2949,17 @@
       <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G3" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="I3" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>237</v>
       </c>
@@ -1976,8 +2978,17 @@
       <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="G4" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="I4" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>239</v>
       </c>
@@ -1996,8 +3007,17 @@
       <c r="F5" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G5" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="I5" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>242</v>
       </c>
@@ -2016,8 +3036,17 @@
       <c r="F6" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G6" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="I6" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>244</v>
       </c>
@@ -2036,8 +3065,17 @@
       <c r="F7" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G7" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="I7" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>246</v>
       </c>
@@ -2056,8 +3094,17 @@
       <c r="F8" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G8" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="I8" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
@@ -2076,8 +3123,17 @@
       <c r="F9" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G9" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="I9" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
@@ -2096,8 +3152,17 @@
       <c r="F10" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G10" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="I10" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -2116,8 +3181,17 @@
       <c r="F11" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G11" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="I11" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
@@ -2136,8 +3210,17 @@
       <c r="F12" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G12" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="I12" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
@@ -2156,8 +3239,17 @@
       <c r="F13" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G13" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="I13" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
@@ -2176,8 +3268,17 @@
       <c r="F14" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G14" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="I14" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>248</v>
       </c>
@@ -2196,8 +3297,17 @@
       <c r="F15" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G15" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="I15" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>250</v>
       </c>
@@ -2216,8 +3326,17 @@
       <c r="F16" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G16" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="I16" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>252</v>
       </c>
@@ -2236,8 +3355,17 @@
       <c r="F17" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G17" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="I17" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>254</v>
       </c>
@@ -2256,8 +3384,17 @@
       <c r="F18" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G18" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="I18" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -2276,8 +3413,17 @@
       <c r="F19" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G19" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="I19" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="360" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>256</v>
       </c>
@@ -2296,8 +3442,17 @@
       <c r="F20" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G20" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="I20" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -2316,8 +3471,17 @@
       <c r="F21" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G21" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="I21" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>22</v>
       </c>
@@ -2336,8 +3500,17 @@
       <c r="F22" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G22" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="I22" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>24</v>
       </c>
@@ -2356,8 +3529,17 @@
       <c r="F23" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G23" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="I23" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>258</v>
       </c>
@@ -2376,8 +3558,17 @@
       <c r="F24" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G24" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="I24" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>26</v>
       </c>
@@ -2396,8 +3587,17 @@
       <c r="F25" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G25" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="I25" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>28</v>
       </c>
@@ -2416,8 +3616,17 @@
       <c r="F26" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G26" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="I26" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>260</v>
       </c>
@@ -2436,8 +3645,17 @@
       <c r="F27" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G27" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="I27" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>262</v>
       </c>
@@ -2456,8 +3674,17 @@
       <c r="F28" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G28" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="I28" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>30</v>
       </c>
@@ -2476,8 +3703,17 @@
       <c r="F29" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G29" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="I29" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>32</v>
       </c>
@@ -2496,8 +3732,17 @@
       <c r="F30" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G30" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="I30" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>35</v>
       </c>
@@ -2516,8 +3761,17 @@
       <c r="F31" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G31" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="I31" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>264</v>
       </c>
@@ -2536,8 +3790,17 @@
       <c r="F32" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G32" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="I32" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>266</v>
       </c>
@@ -2556,8 +3819,17 @@
       <c r="F33" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G33" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="I33" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>268</v>
       </c>
@@ -2576,8 +3848,17 @@
       <c r="F34" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G34" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="I34" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="144" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>270</v>
       </c>
@@ -2596,8 +3877,17 @@
       <c r="F35" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G35" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="I35" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>272</v>
       </c>
@@ -2616,8 +3906,17 @@
       <c r="F36" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G36" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="I36" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>274</v>
       </c>
@@ -2636,8 +3935,17 @@
       <c r="F37" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G37" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="I37" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>276</v>
       </c>
@@ -2656,8 +3964,17 @@
       <c r="F38" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G38" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="I38" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>278</v>
       </c>
@@ -2676,8 +3993,17 @@
       <c r="F39" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G39" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="I39" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>280</v>
       </c>
@@ -2696,8 +4022,17 @@
       <c r="F40" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G40" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="I40" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>282</v>
       </c>
@@ -2716,8 +4051,17 @@
       <c r="F41" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G41" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="I41" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>37</v>
       </c>
@@ -2736,8 +4080,17 @@
       <c r="F42" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G42" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="I42" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="360" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>39</v>
       </c>
@@ -2756,8 +4109,17 @@
       <c r="F43" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G43" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="I43" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>41</v>
       </c>
@@ -2776,8 +4138,17 @@
       <c r="F44" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G44" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="I44" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="216" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>43</v>
       </c>
@@ -2796,8 +4167,17 @@
       <c r="F45" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G45" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="I45" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>45</v>
       </c>
@@ -2816,8 +4196,17 @@
       <c r="F46" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G46" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="I46" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>284</v>
       </c>
@@ -2836,8 +4225,17 @@
       <c r="F47" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G47" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="I47" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>287</v>
       </c>
@@ -2856,8 +4254,17 @@
       <c r="F48" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G48" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="I48" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>290</v>
       </c>
@@ -2876,8 +4283,17 @@
       <c r="F49" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G49" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="I49" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>293</v>
       </c>
@@ -2896,8 +4312,17 @@
       <c r="F50" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G50" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="I50" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>296</v>
       </c>
@@ -2916,8 +4341,17 @@
       <c r="F51" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G51" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="I51" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>298</v>
       </c>
@@ -2936,8 +4370,17 @@
       <c r="F52" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G52" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="I52" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>300</v>
       </c>
@@ -2956,8 +4399,17 @@
       <c r="F53" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G53" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="I53" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>302</v>
       </c>
@@ -2976,8 +4428,17 @@
       <c r="F54" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G54" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="I54" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>305</v>
       </c>
@@ -2996,8 +4457,17 @@
       <c r="F55" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G55" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="I55" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>307</v>
       </c>
@@ -3016,8 +4486,17 @@
       <c r="F56" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G56" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="I56" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>47</v>
       </c>
@@ -3036,8 +4515,17 @@
       <c r="F57" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G57" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="I57" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>49</v>
       </c>
@@ -3056,8 +4544,17 @@
       <c r="F58" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G58" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="I58" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>51</v>
       </c>
@@ -3076,8 +4573,17 @@
       <c r="F59" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G59" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="I59" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>53</v>
       </c>
@@ -3096,8 +4602,17 @@
       <c r="F60" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G60" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="I60" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>54</v>
       </c>
@@ -3116,8 +4631,17 @@
       <c r="F61" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G61" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="I61" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>55</v>
       </c>
@@ -3136,8 +4660,17 @@
       <c r="F62" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G62" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="I62" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="216" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>56</v>
       </c>
@@ -3156,8 +4689,17 @@
       <c r="F63" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G63" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="I63" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>309</v>
       </c>
@@ -3176,8 +4718,17 @@
       <c r="F64" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G64" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="I64" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>312</v>
       </c>
@@ -3196,8 +4747,17 @@
       <c r="F65" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G65" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="I65" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>57</v>
       </c>
@@ -3216,8 +4776,17 @@
       <c r="F66" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G66" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="I66" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>314</v>
       </c>
@@ -3236,8 +4805,17 @@
       <c r="F67" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G67" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="I67" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>316</v>
       </c>
@@ -3256,8 +4834,17 @@
       <c r="F68" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G68" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="I68" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>58</v>
       </c>
@@ -3276,8 +4863,17 @@
       <c r="F69" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G69" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="I69" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>60</v>
       </c>
@@ -3296,8 +4892,17 @@
       <c r="F70" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G70" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="I70" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>62</v>
       </c>
@@ -3316,8 +4921,17 @@
       <c r="F71" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G71" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="I71" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>64</v>
       </c>
@@ -3336,8 +4950,17 @@
       <c r="F72" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G72" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="I72" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>66</v>
       </c>
@@ -3356,8 +4979,17 @@
       <c r="F73" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G73" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="I73" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>68</v>
       </c>
@@ -3376,8 +5008,17 @@
       <c r="F74" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G74" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="I74" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>318</v>
       </c>
@@ -3396,8 +5037,17 @@
       <c r="F75" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G75" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="I75" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>320</v>
       </c>
@@ -3416,8 +5066,17 @@
       <c r="F76" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G76" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="I76" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>322</v>
       </c>
@@ -3436,8 +5095,17 @@
       <c r="F77" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G77" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="I77" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>324</v>
       </c>
@@ -3456,8 +5124,17 @@
       <c r="F78" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G78" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="I78" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>326</v>
       </c>
@@ -3476,8 +5153,17 @@
       <c r="F79" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G79" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="I79" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>328</v>
       </c>
@@ -3496,8 +5182,17 @@
       <c r="F80" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G80" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="I80" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>70</v>
       </c>
@@ -3516,8 +5211,17 @@
       <c r="F81" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G81" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="I81" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>72</v>
       </c>
@@ -3536,8 +5240,17 @@
       <c r="F82" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G82" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="I82" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>74</v>
       </c>
@@ -3556,8 +5269,17 @@
       <c r="F83" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G83" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="I83" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>76</v>
       </c>
@@ -3576,8 +5298,17 @@
       <c r="F84" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G84" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="I84" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="144" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>78</v>
       </c>
@@ -3596,8 +5327,17 @@
       <c r="F85" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G85" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="I85" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>80</v>
       </c>
@@ -3616,8 +5356,17 @@
       <c r="F86" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G86" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="I86" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>82</v>
       </c>
@@ -3636,8 +5385,17 @@
       <c r="F87" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G87" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="I87" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>84</v>
       </c>
@@ -3656,8 +5414,17 @@
       <c r="F88" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G88" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="I88" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>330</v>
       </c>
@@ -3676,8 +5443,17 @@
       <c r="F89" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G89" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="I89" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>332</v>
       </c>
@@ -3696,8 +5472,17 @@
       <c r="F90" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G90" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="I90" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="216" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>86</v>
       </c>
@@ -3716,8 +5501,17 @@
       <c r="F91" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G91" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="I91" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>88</v>
       </c>
@@ -3736,8 +5530,17 @@
       <c r="F92" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G92" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="I92" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>90</v>
       </c>
@@ -3756,8 +5559,17 @@
       <c r="F93" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G93" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="I93" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>92</v>
       </c>
@@ -3776,8 +5588,17 @@
       <c r="F94" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G94" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="I94" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>334</v>
       </c>
@@ -3796,8 +5617,17 @@
       <c r="F95" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G95" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="I95" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>336</v>
       </c>
@@ -3816,8 +5646,17 @@
       <c r="F96" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G96" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="I96" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="216" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>338</v>
       </c>
@@ -3836,8 +5675,17 @@
       <c r="F97" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G97" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="I97" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>340</v>
       </c>
@@ -3856,8 +5704,17 @@
       <c r="F98" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G98" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="I98" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>342</v>
       </c>
@@ -3876,8 +5733,17 @@
       <c r="F99" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G99" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="I99" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>94</v>
       </c>
@@ -3896,8 +5762,17 @@
       <c r="F100" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="101" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G100" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="I100" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="288" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>344</v>
       </c>
@@ -3916,8 +5791,17 @@
       <c r="F101" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G101" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="I101" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>346</v>
       </c>
@@ -3936,8 +5820,17 @@
       <c r="F102" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="103" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G102" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="I102" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>348</v>
       </c>
@@ -3956,8 +5849,17 @@
       <c r="F103" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="104" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G103" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="I103" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="216" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>350</v>
       </c>
@@ -3976,8 +5878,17 @@
       <c r="F104" s="1" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="105" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G104" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="I104" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>352</v>
       </c>
@@ -3996,8 +5907,17 @@
       <c r="F105" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="106" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G105" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="I105" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>354</v>
       </c>
@@ -4016,8 +5936,17 @@
       <c r="F106" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="107" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G106" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="I106" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="216" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>356</v>
       </c>
@@ -4036,8 +5965,17 @@
       <c r="F107" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G107" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="I107" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>96</v>
       </c>
@@ -4056,8 +5994,17 @@
       <c r="F108" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="109" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G108" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="I108" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>98</v>
       </c>
@@ -4076,8 +6023,17 @@
       <c r="F109" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="110" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G109" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="I109" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>100</v>
       </c>
@@ -4096,8 +6052,17 @@
       <c r="F110" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="111" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G110" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="I110" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>102</v>
       </c>
@@ -4116,8 +6081,17 @@
       <c r="F111" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="112" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G111" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="I111" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>105</v>
       </c>
@@ -4136,8 +6110,17 @@
       <c r="F112" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="113" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G112" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="I112" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>358</v>
       </c>
@@ -4156,8 +6139,17 @@
       <c r="F113" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="114" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G113" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="I113" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>360</v>
       </c>
@@ -4176,8 +6168,17 @@
       <c r="F114" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G114" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="I114" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>362</v>
       </c>
@@ -4196,8 +6197,17 @@
       <c r="F115" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G115" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="I115" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>364</v>
       </c>
@@ -4216,8 +6226,17 @@
       <c r="F116" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="117" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G116" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="I116" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>367</v>
       </c>
@@ -4236,8 +6255,17 @@
       <c r="F117" s="1" t="s">
         <v>362</v>
       </c>
-    </row>
-    <row r="118" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G117" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="I117" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>108</v>
       </c>
@@ -4256,8 +6284,17 @@
       <c r="F118" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="119" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G118" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="I118" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>370</v>
       </c>
@@ -4276,8 +6313,17 @@
       <c r="F119" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="120" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G119" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="I119" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>110</v>
       </c>
@@ -4296,8 +6342,17 @@
       <c r="F120" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="121" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G120" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="I120" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>112</v>
       </c>
@@ -4316,8 +6371,17 @@
       <c r="F121" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="122" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G121" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="I121" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>114</v>
       </c>
@@ -4336,8 +6400,17 @@
       <c r="F122" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G122" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="I122" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>116</v>
       </c>
@@ -4356,8 +6429,17 @@
       <c r="F123" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G123" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="I123" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>118</v>
       </c>
@@ -4376,8 +6458,17 @@
       <c r="F124" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="125" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G124" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="I124" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>120</v>
       </c>
@@ -4396,8 +6487,17 @@
       <c r="F125" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="126" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G125" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="I125" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>374</v>
       </c>
@@ -4416,8 +6516,17 @@
       <c r="F126" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G126" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="I126" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>122</v>
       </c>
@@ -4436,8 +6545,17 @@
       <c r="F127" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="128" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G127" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="I127" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>376</v>
       </c>
@@ -4456,8 +6574,17 @@
       <c r="F128" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="129" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G128" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="I128" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>378</v>
       </c>
@@ -4476,8 +6603,17 @@
       <c r="F129" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="130" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G129" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="I129" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>124</v>
       </c>
@@ -4496,8 +6632,17 @@
       <c r="F130" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="131" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G130" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="I130" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>126</v>
       </c>
@@ -4516,8 +6661,17 @@
       <c r="F131" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="132" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G131" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="I131" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>128</v>
       </c>
@@ -4536,8 +6690,17 @@
       <c r="F132" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="133" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G132" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="I132" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>130</v>
       </c>
@@ -4556,8 +6719,17 @@
       <c r="F133" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="134" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G133" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="I133" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>132</v>
       </c>
@@ -4576,8 +6748,17 @@
       <c r="F134" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="135" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G134" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="I134" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>134</v>
       </c>
@@ -4596,8 +6777,17 @@
       <c r="F135" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="136" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G135" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="I135" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>136</v>
       </c>
@@ -4616,8 +6806,17 @@
       <c r="F136" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="137" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G136" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="I136" s="7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>380</v>
       </c>
@@ -4636,8 +6835,17 @@
       <c r="F137" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="138" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G137" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="I137" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>382</v>
       </c>
@@ -4656,8 +6864,17 @@
       <c r="F138" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="139" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G138" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="I138" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>384</v>
       </c>
@@ -4676,8 +6893,17 @@
       <c r="F139" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="140" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G139" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="I139" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>386</v>
       </c>
@@ -4696,8 +6922,17 @@
       <c r="F140" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="141" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G140" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H140" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="I140" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>388</v>
       </c>
@@ -4716,8 +6951,17 @@
       <c r="F141" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="142" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G141" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H141" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="I141" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>390</v>
       </c>
@@ -4736,8 +6980,17 @@
       <c r="F142" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="143" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G142" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H142" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="I142" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>392</v>
       </c>
@@ -4756,8 +7009,17 @@
       <c r="F143" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="144" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G143" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H143" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="I143" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>394</v>
       </c>
@@ -4776,8 +7038,17 @@
       <c r="F144" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="145" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G144" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="I144" s="7">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>396</v>
       </c>
@@ -4796,8 +7067,17 @@
       <c r="F145" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="146" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G145" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="H145" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="I145" s="7">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>398</v>
       </c>
@@ -4816,8 +7096,17 @@
       <c r="F146" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="147" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G146" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="H146" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="I146" s="7">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>400</v>
       </c>
@@ -4836,8 +7125,17 @@
       <c r="F147" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="148" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G147" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="H147" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="I147" s="7">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>402</v>
       </c>
@@ -4856,8 +7154,17 @@
       <c r="F148" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="149" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G148" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="H148" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="I148" s="7">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>404</v>
       </c>
@@ -4876,8 +7183,17 @@
       <c r="F149" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="150" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G149" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="I149" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>406</v>
       </c>
@@ -4896,8 +7212,17 @@
       <c r="F150" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="151" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G150" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H150" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="I150" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="144" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>408</v>
       </c>
@@ -4916,8 +7241,17 @@
       <c r="F151" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="152" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G151" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H151" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="I151" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>410</v>
       </c>
@@ -4936,8 +7270,17 @@
       <c r="F152" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="153" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G152" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H152" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="I152" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>412</v>
       </c>
@@ -4956,8 +7299,17 @@
       <c r="F153" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="154" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G153" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H153" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="I153" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>414</v>
       </c>
@@ -4976,8 +7328,17 @@
       <c r="F154" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="155" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G154" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H154" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="I154" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="216" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>416</v>
       </c>
@@ -4996,8 +7357,17 @@
       <c r="F155" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="156" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G155" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="H155" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="I155" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>418</v>
       </c>
@@ -5016,8 +7386,17 @@
       <c r="F156" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="157" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G156" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H156" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="I156" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>137</v>
       </c>
@@ -5036,8 +7415,17 @@
       <c r="F157" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="158" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G157" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H157" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="I157" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>139</v>
       </c>
@@ -5056,8 +7444,17 @@
       <c r="F158" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="159" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G158" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H158" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="I158" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>141</v>
       </c>
@@ -5076,8 +7473,17 @@
       <c r="F159" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="160" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G159" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H159" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="I159" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>143</v>
       </c>
@@ -5096,8 +7502,17 @@
       <c r="F160" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="161" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G160" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H160" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="I160" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>421</v>
       </c>
@@ -5116,8 +7531,17 @@
       <c r="F161" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="162" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G161" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H161" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="I161" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>423</v>
       </c>
@@ -5136,8 +7560,17 @@
       <c r="F162" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="163" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="G162" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H162" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="I162" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="216" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>425</v>
       </c>
@@ -5156,8 +7589,17 @@
       <c r="F163" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="164" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G163" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H163" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="I163" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>427</v>
       </c>
@@ -5176,8 +7618,17 @@
       <c r="F164" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="165" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G164" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="H164" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="I164" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>429</v>
       </c>
@@ -5196,8 +7647,17 @@
       <c r="F165" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="166" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G165" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H165" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="I165" s="7" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>432</v>
       </c>
@@ -5216,8 +7676,17 @@
       <c r="F166" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="167" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G166" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H166" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="I166" s="7" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>435</v>
       </c>
@@ -5236,8 +7705,17 @@
       <c r="F167" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="168" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G167" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H167" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="I167" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>437</v>
       </c>
@@ -5256,8 +7734,17 @@
       <c r="F168" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="169" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G168" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H168" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="I168" s="7">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>440</v>
       </c>
@@ -5276,8 +7763,17 @@
       <c r="F169" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="170" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G169" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H169" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="I169" s="7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" ht="216" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>145</v>
       </c>
@@ -5296,8 +7792,17 @@
       <c r="F170" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="171" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G170" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H170" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="I170" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>146</v>
       </c>
@@ -5316,8 +7821,17 @@
       <c r="F171" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="172" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G171" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H171" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="I171" s="7">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" ht="144" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>442</v>
       </c>
@@ -5336,8 +7850,17 @@
       <c r="F172" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="173" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G172" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H172" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="I172" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>444</v>
       </c>
@@ -5356,8 +7879,17 @@
       <c r="F173" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="174" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G173" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H173" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="I173" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>446</v>
       </c>
@@ -5376,8 +7908,17 @@
       <c r="F174" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="175" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G174" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="H174" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="I174" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" ht="144" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>448</v>
       </c>
@@ -5396,8 +7937,17 @@
       <c r="F175" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="176" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G175" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H175" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="I175" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>450</v>
       </c>
@@ -5416,8 +7966,17 @@
       <c r="F176" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="177" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G176" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H176" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="I176" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>452</v>
       </c>
@@ -5436,8 +7995,17 @@
       <c r="F177" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="178" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G177" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H177" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="I177" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>454</v>
       </c>
@@ -5456,8 +8024,17 @@
       <c r="F178" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="179" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G178" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H178" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="I178" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>456</v>
       </c>
@@ -5476,8 +8053,17 @@
       <c r="F179" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="180" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G179" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H179" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="I179" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>458</v>
       </c>
@@ -5496,8 +8082,17 @@
       <c r="F180" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="181" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G180" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H180" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="I180" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>460</v>
       </c>
@@ -5516,8 +8111,17 @@
       <c r="F181" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="182" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G181" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H181" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="I181" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>462</v>
       </c>
@@ -5536,8 +8140,17 @@
       <c r="F182" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="183" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G182" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H182" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="I182" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>148</v>
       </c>
@@ -5556,8 +8169,17 @@
       <c r="F183" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="184" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G183" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="H183" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="I183" s="7" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>465</v>
       </c>
@@ -5576,8 +8198,17 @@
       <c r="F184" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="185" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G184" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="H184" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="I184" s="7" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>467</v>
       </c>
@@ -5596,8 +8227,17 @@
       <c r="F185" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="186" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G185" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="H185" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="I185" s="7" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>469</v>
       </c>
@@ -5616,8 +8256,17 @@
       <c r="F186" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="187" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G186" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="H186" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="I186" s="7" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>471</v>
       </c>
@@ -5636,8 +8285,17 @@
       <c r="F187" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="188" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G187" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="H187" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="I187" s="7" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>473</v>
       </c>
@@ -5656,8 +8314,17 @@
       <c r="F188" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="189" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G188" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="H188" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="I188" s="7" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>476</v>
       </c>
@@ -5676,8 +8343,17 @@
       <c r="F189" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="190" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G189" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="H189" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="I189" s="7" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>478</v>
       </c>
@@ -5696,8 +8372,17 @@
       <c r="F190" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="191" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G190" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="H190" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="I190" s="7" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>480</v>
       </c>
@@ -5716,8 +8401,17 @@
       <c r="F191" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="192" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G191" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="H191" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="I191" s="7" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>482</v>
       </c>
@@ -5736,8 +8430,17 @@
       <c r="F192" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="193" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G192" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="H192" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="I192" s="7" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>484</v>
       </c>
@@ -5756,8 +8459,17 @@
       <c r="F193" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="194" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G193" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H193" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="I193" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>151</v>
       </c>
@@ -5776,8 +8488,17 @@
       <c r="F194" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="195" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G194" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="H194" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="I194" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>153</v>
       </c>
@@ -5796,8 +8517,17 @@
       <c r="F195" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="196" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G195" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="H195" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="I195" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>155</v>
       </c>
@@ -5816,8 +8546,17 @@
       <c r="F196" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="197" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G196" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="H196" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="I196" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>157</v>
       </c>
@@ -5836,8 +8575,17 @@
       <c r="F197" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="198" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G197" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="H197" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="I197" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>159</v>
       </c>
@@ -5856,8 +8604,17 @@
       <c r="F198" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="199" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G198" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H198" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="I198" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>161</v>
       </c>
@@ -5876,8 +8633,17 @@
       <c r="F199" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="200" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G199" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H199" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="I199" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>487</v>
       </c>
@@ -5896,8 +8662,17 @@
       <c r="F200" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="201" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G200" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H200" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="I200" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>489</v>
       </c>
@@ -5916,8 +8691,17 @@
       <c r="F201" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="202" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G201" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H201" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="I201" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>491</v>
       </c>
@@ -5936,8 +8720,17 @@
       <c r="F202" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="203" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G202" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H202" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="I202" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>493</v>
       </c>
@@ -5956,8 +8749,17 @@
       <c r="F203" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="204" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="G203" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="H203" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="I203" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>495</v>
       </c>
@@ -5976,8 +8778,17 @@
       <c r="F204" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="205" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="G204" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="H204" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="I204" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>164</v>
       </c>
@@ -5996,8 +8807,17 @@
       <c r="F205" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="206" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G205" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H205" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="I205" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>167</v>
       </c>
@@ -6016,8 +8836,17 @@
       <c r="F206" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="207" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G206" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="H206" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="I206" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>497</v>
       </c>
@@ -6036,8 +8865,17 @@
       <c r="F207" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="208" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G207" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="H207" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="I207" s="7">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>169</v>
       </c>
@@ -6056,8 +8894,17 @@
       <c r="F208" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="209" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G208" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="H208" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="I208" s="7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>500</v>
       </c>
@@ -6076,8 +8923,17 @@
       <c r="F209" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="210" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G209" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H209" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="I209" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>502</v>
       </c>
@@ -6096,8 +8952,17 @@
       <c r="F210" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="211" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G210" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="H210" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="I210" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>172</v>
       </c>
@@ -6116,8 +8981,17 @@
       <c r="F211" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="212" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G211" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H211" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="I211" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>174</v>
       </c>
@@ -6136,8 +9010,17 @@
       <c r="F212" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="213" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G212" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H212" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="I212" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>176</v>
       </c>
@@ -6156,8 +9039,17 @@
       <c r="F213" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="214" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G213" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H213" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="I213" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>178</v>
       </c>
@@ -6176,8 +9068,17 @@
       <c r="F214" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="215" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G214" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="H214" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="I214" s="7">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>505</v>
       </c>
@@ -6196,8 +9097,17 @@
       <c r="F215" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="216" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G215" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H215" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="I215" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>507</v>
       </c>
@@ -6216,8 +9126,17 @@
       <c r="F216" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="217" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="G216" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="H216" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="I216" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>180</v>
       </c>
@@ -6236,8 +9155,17 @@
       <c r="F217" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="218" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="G217" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H217" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="I217" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>182</v>
       </c>
@@ -6255,6 +9183,15 @@
       </c>
       <c r="F218" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="G218" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="H218" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="I218" s="7">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
